--- a/output/台指期籌碼追蹤.xlsx
+++ b/output/台指期籌碼追蹤.xlsx
@@ -21,7 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Calibri"/>
@@ -108,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -136,9 +138,11 @@
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -25564,7 +25568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25575,7 +25579,9 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25621,6 +25627,16 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>帳戶餘額</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>報酬率(%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>勝負</t>
         </is>
       </c>
@@ -25654,7 +25670,13 @@
       <c r="H2" s="3" t="n">
         <v>118336</v>
       </c>
-      <c r="I2" s="14" t="inlineStr">
+      <c r="I2" s="3" t="n">
+        <v>268336</v>
+      </c>
+      <c r="J2" s="25" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
@@ -25689,7 +25711,13 @@
       <c r="H3" s="3" t="n">
         <v>120222</v>
       </c>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="I3" s="3" t="n">
+        <v>270222</v>
+      </c>
+      <c r="J3" s="25" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
@@ -25724,7 +25752,13 @@
       <c r="H4" s="3" t="n">
         <v>160408</v>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="3" t="n">
+        <v>310408</v>
+      </c>
+      <c r="J4" s="25" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
@@ -25759,7 +25793,13 @@
       <c r="H5" s="3" t="n">
         <v>152244</v>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="3" t="n">
+        <v>302244</v>
+      </c>
+      <c r="J5" s="25" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
@@ -25794,7 +25834,13 @@
       <c r="H6" s="3" t="n">
         <v>173030</v>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="3" t="n">
+        <v>323030</v>
+      </c>
+      <c r="J6" s="25" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
@@ -25829,7 +25875,13 @@
       <c r="H7" s="3" t="n">
         <v>145666</v>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="3" t="n">
+        <v>295666</v>
+      </c>
+      <c r="J7" s="25" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="K7" s="26" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
@@ -25864,7 +25916,13 @@
       <c r="H8" s="3" t="n">
         <v>136802</v>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="3" t="n">
+        <v>286802</v>
+      </c>
+      <c r="J8" s="25" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
@@ -25899,7 +25957,13 @@
       <c r="H9" s="3" t="n">
         <v>176038</v>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="3" t="n">
+        <v>326038</v>
+      </c>
+      <c r="J9" s="25" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
@@ -25934,7 +25998,13 @@
       <c r="H10" s="3" t="n">
         <v>282624</v>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="3" t="n">
+        <v>432624</v>
+      </c>
+      <c r="J10" s="25" t="n">
+        <v>188.4</v>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
@@ -25969,7 +26039,13 @@
       <c r="H11" s="3" t="n">
         <v>381610</v>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="3" t="n">
+        <v>531610</v>
+      </c>
+      <c r="J11" s="25" t="n">
+        <v>254.4</v>
+      </c>
+      <c r="K11" s="14" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
@@ -26004,7 +26080,13 @@
       <c r="H12" s="3" t="n">
         <v>378496</v>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I12" s="3" t="n">
+        <v>528496</v>
+      </c>
+      <c r="J12" s="25" t="n">
+        <v>252.3</v>
+      </c>
+      <c r="K12" s="26" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
@@ -26039,7 +26121,13 @@
       <c r="H13" s="3" t="n">
         <v>438982</v>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="3" t="n">
+        <v>588982</v>
+      </c>
+      <c r="J13" s="25" t="n">
+        <v>292.7</v>
+      </c>
+      <c r="K13" s="14" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
@@ -26074,7 +26162,13 @@
       <c r="H14" s="3" t="n">
         <v>476818</v>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="3" t="n">
+        <v>626818</v>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>317.9</v>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
@@ -26109,7 +26203,13 @@
       <c r="H15" s="3" t="n">
         <v>608354</v>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="3" t="n">
+        <v>758354</v>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>405.6</v>
+      </c>
+      <c r="K15" s="14" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
@@ -26144,7 +26244,13 @@
       <c r="H16" s="3" t="n">
         <v>653490</v>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="3" t="n">
+        <v>803490</v>
+      </c>
+      <c r="J16" s="25" t="n">
+        <v>435.7</v>
+      </c>
+      <c r="K16" s="14" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
@@ -26179,33 +26285,45 @@
       <c r="H17" s="3" t="n">
         <v>681476</v>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="3" t="n">
+        <v>831476</v>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>454.3</v>
+      </c>
+      <c r="K17" s="14" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>16筆</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>勝率75.0%</t>
         </is>
       </c>
-      <c r="F18" s="27" t="n">
+      <c r="F18" s="28" t="n">
         <v>13666</v>
       </c>
-      <c r="G18" s="27" t="n">
+      <c r="G18" s="28" t="n">
         <v>681476</v>
+      </c>
+      <c r="I18" s="28" t="n">
+        <v>831476</v>
+      </c>
+      <c r="J18" s="29" t="n">
+        <v>454.3</v>
       </c>
     </row>
   </sheetData>
@@ -26604,7 +26722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -26614,6 +26732,8 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26652,6 +26772,16 @@
           <t>年損益金額</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>年初餘額</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>年報酬率(%)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -26675,6 +26805,12 @@
       <c r="G2" s="3" t="n">
         <v>145666</v>
       </c>
+      <c r="H2" s="3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>97.09999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -26698,6 +26834,12 @@
       <c r="G3" s="3" t="n">
         <v>331152</v>
       </c>
+      <c r="H3" s="3" t="n">
+        <v>295666</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -26720,6 +26862,12 @@
       </c>
       <c r="G4" s="3" t="n">
         <v>204658</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>626818</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>32.7</v>
       </c>
     </row>
   </sheetData>
@@ -26753,72 +26901,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="28" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>近月_ours</t>
         </is>
       </c>
-      <c r="C1" s="28" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>近月_correct</t>
         </is>
       </c>
-      <c r="D1" s="28" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>近月_diff</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>遠月_ours</t>
         </is>
       </c>
-      <c r="F1" s="28" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>遠月_correct</t>
         </is>
       </c>
-      <c r="G1" s="28" t="inlineStr">
+      <c r="G1" s="30" t="inlineStr">
         <is>
           <t>遠月_diff</t>
         </is>
       </c>
-      <c r="H1" s="28" t="inlineStr">
+      <c r="H1" s="30" t="inlineStr">
         <is>
           <t>小散戶_ours</t>
         </is>
       </c>
-      <c r="I1" s="28" t="inlineStr">
+      <c r="I1" s="30" t="inlineStr">
         <is>
           <t>小散戶_correct</t>
         </is>
       </c>
-      <c r="J1" s="28" t="inlineStr">
+      <c r="J1" s="30" t="inlineStr">
         <is>
           <t>小散戶_diff</t>
         </is>
       </c>
-      <c r="K1" s="28" t="inlineStr">
+      <c r="K1" s="30" t="inlineStr">
         <is>
           <t>主力_ours</t>
         </is>
       </c>
-      <c r="L1" s="28" t="inlineStr">
+      <c r="L1" s="30" t="inlineStr">
         <is>
           <t>主力_correct</t>
         </is>
       </c>
-      <c r="M1" s="28" t="inlineStr">
+      <c r="M1" s="30" t="inlineStr">
         <is>
           <t>主力_diff</t>
         </is>
       </c>
-      <c r="N1" s="28" t="inlineStr">
+      <c r="N1" s="30" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
@@ -27034,7 +27182,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>台指期籌碼策略（v2 優化版）</t>
         </is>
@@ -27044,7 +27192,7 @@
       <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>【資料來源】100% 期交所</t>
         </is>
@@ -27075,7 +27223,7 @@
       <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>【公式】</t>
         </is>
@@ -27120,7 +27268,7 @@
       <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>【策略（v2 優化版）】</t>
         </is>
@@ -27151,7 +27299,7 @@
       <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>【信號說明】</t>
         </is>
@@ -27210,7 +27358,7 @@
       <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>【操作欄說明】</t>
         </is>
@@ -27258,7 +27406,7 @@
       <c r="A36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>【改善原因】</t>
         </is>
@@ -27282,7 +27430,7 @@
       <c r="A40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="30" t="inlineStr">
+      <c r="A41" s="32" t="inlineStr">
         <is>
           <t>【成本】</t>
         </is>

--- a/output/台指期籌碼追蹤.xlsx
+++ b/output/台指期籌碼追蹤.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O516"/>
+  <dimension ref="A1:O517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -646,9 +646,7 @@
       <c r="J2" s="4" t="n">
         <v>-10845</v>
       </c>
-      <c r="K2" s="3" t="n">
-        <v/>
-      </c>
+      <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
@@ -695,9 +693,7 @@
       <c r="J3" s="4" t="n">
         <v>-52403</v>
       </c>
-      <c r="K3" s="3" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
@@ -744,9 +740,7 @@
       <c r="J4" s="4" t="n">
         <v>-32058</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
@@ -793,9 +787,7 @@
       <c r="J5" s="4" t="n">
         <v>-33290</v>
       </c>
-      <c r="K5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
@@ -842,9 +834,7 @@
       <c r="J6" s="4" t="n">
         <v>-27945.5</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
@@ -27535,6 +27525,57 @@
         </is>
       </c>
       <c r="O516" s="5" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>2026/03/20</t>
+        </is>
+      </c>
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C517" s="3" t="n">
+        <v>33809</v>
+      </c>
+      <c r="D517" s="3" t="n">
+        <v>33559</v>
+      </c>
+      <c r="E517" s="3" t="n">
+        <v>4220</v>
+      </c>
+      <c r="F517" s="3" t="n">
+        <v>3632</v>
+      </c>
+      <c r="G517" s="3" t="n">
+        <v>-37</v>
+      </c>
+      <c r="H517" s="3" t="n">
+        <v>22863</v>
+      </c>
+      <c r="I517" s="3" t="n">
+        <v>4257</v>
+      </c>
+      <c r="J517" s="4" t="n">
+        <v>-21010</v>
+      </c>
+      <c r="K517" s="7" t="n">
+        <v>13736</v>
+      </c>
+      <c r="L517" s="2" t="inlineStr"/>
+      <c r="M517" s="2" t="inlineStr"/>
+      <c r="N517" s="2" t="inlineStr">
+        <is>
+          <t>⬇️空方</t>
+        </is>
+      </c>
+      <c r="O517" s="5" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
@@ -29171,9 +29212,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="36" t="inlineStr">
         <is>
@@ -29202,9 +29241,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="36" t="inlineStr">
         <is>
@@ -29247,9 +29284,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
@@ -29278,9 +29313,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="36" t="inlineStr">
         <is>
@@ -29337,9 +29370,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="36" t="inlineStr">
         <is>
@@ -29375,9 +29406,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -29385,9 +29414,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="36" t="inlineStr">
         <is>
@@ -29409,9 +29436,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="36" t="inlineStr">
         <is>

--- a/output/台指期籌碼追蹤.xlsx
+++ b/output/台指期籌碼追蹤.xlsx
@@ -646,7 +646,9 @@
       <c r="J2" s="4" t="n">
         <v>-10845</v>
       </c>
-      <c r="K2" s="3" t="n"/>
+      <c r="K2" s="3" t="n">
+        <v/>
+      </c>
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
@@ -693,7 +695,9 @@
       <c r="J3" s="4" t="n">
         <v>-52403</v>
       </c>
-      <c r="K3" s="3" t="n"/>
+      <c r="K3" s="3" t="n">
+        <v/>
+      </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
@@ -740,7 +744,9 @@
       <c r="J4" s="4" t="n">
         <v>-32058</v>
       </c>
-      <c r="K4" s="3" t="n"/>
+      <c r="K4" s="3" t="n">
+        <v/>
+      </c>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +793,9 @@
       <c r="J5" s="4" t="n">
         <v>-33290</v>
       </c>
-      <c r="K5" s="3" t="n"/>
+      <c r="K5" s="3" t="n">
+        <v/>
+      </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
@@ -834,7 +842,9 @@
       <c r="J6" s="4" t="n">
         <v>-27945.5</v>
       </c>
-      <c r="K6" s="3" t="n"/>
+      <c r="K6" s="3" t="n">
+        <v/>
+      </c>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
@@ -27568,7 +27578,7 @@
       <c r="K517" s="7" t="n">
         <v>13736</v>
       </c>
-      <c r="L517" s="2" t="inlineStr"/>
+      <c r="L517" s="3" t="inlineStr"/>
       <c r="M517" s="2" t="inlineStr"/>
       <c r="N517" s="2" t="inlineStr">
         <is>
@@ -28361,7 +28371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28371,6 +28381,8 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28409,6 +28421,16 @@
           <t>月損益金額</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>月初餘額</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>月報酬率(%)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -28434,6 +28456,12 @@
       <c r="G2" s="14" t="n">
         <v>118336</v>
       </c>
+      <c r="H2" s="3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>78.90000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -28459,6 +28487,12 @@
       <c r="G3" s="14" t="n">
         <v>1886</v>
       </c>
+      <c r="H3" s="3" t="n">
+        <v>268336</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -28484,6 +28518,12 @@
       <c r="G4" s="14" t="n">
         <v>40186</v>
       </c>
+      <c r="H4" s="3" t="n">
+        <v>270222</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>14.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -28509,6 +28549,12 @@
       <c r="G5" s="4" t="n">
         <v>-14742</v>
       </c>
+      <c r="H5" s="3" t="n">
+        <v>310408</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>-4.7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -28534,6 +28580,12 @@
       <c r="G6" s="4" t="n">
         <v>-8864</v>
       </c>
+      <c r="H6" s="3" t="n">
+        <v>295666</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -28559,6 +28611,12 @@
       <c r="G7" s="14" t="n">
         <v>39236</v>
       </c>
+      <c r="H7" s="3" t="n">
+        <v>286802</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>13.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -28584,6 +28642,12 @@
       <c r="G8" s="14" t="n">
         <v>106586</v>
       </c>
+      <c r="H8" s="3" t="n">
+        <v>326038</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>32.7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -28609,6 +28673,12 @@
       <c r="G9" s="14" t="n">
         <v>98986</v>
       </c>
+      <c r="H9" s="3" t="n">
+        <v>432624</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>22.9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -28634,6 +28704,12 @@
       <c r="G10" s="14" t="n">
         <v>57372</v>
       </c>
+      <c r="H10" s="3" t="n">
+        <v>531610</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>10.8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -28659,6 +28735,12 @@
       <c r="G11" s="14" t="n">
         <v>37836</v>
       </c>
+      <c r="H11" s="3" t="n">
+        <v>588982</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -28684,6 +28766,12 @@
       <c r="G12" s="14" t="n">
         <v>131536</v>
       </c>
+      <c r="H12" s="3" t="n">
+        <v>626818</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -28709,6 +28797,12 @@
       <c r="G13" s="14" t="n">
         <v>45136</v>
       </c>
+      <c r="H13" s="3" t="n">
+        <v>758354</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -28733,6 +28827,12 @@
       </c>
       <c r="G14" s="14" t="n">
         <v>27986</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>803490</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
@@ -29212,7 +29312,9 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
     <row r="3">
       <c r="A3" s="36" t="inlineStr">
         <is>
@@ -29241,7 +29343,9 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+    </row>
     <row r="8">
       <c r="A8" s="36" t="inlineStr">
         <is>
@@ -29284,7 +29388,9 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
@@ -29313,7 +29419,9 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+    </row>
     <row r="20">
       <c r="A20" s="36" t="inlineStr">
         <is>
@@ -29370,7 +29478,9 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+    </row>
     <row r="29">
       <c r="A29" s="36" t="inlineStr">
         <is>
@@ -29406,7 +29516,9 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+    </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -29414,7 +29526,9 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+    </row>
     <row r="37">
       <c r="A37" s="36" t="inlineStr">
         <is>
@@ -29436,7 +29550,9 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+    </row>
     <row r="41">
       <c r="A41" s="36" t="inlineStr">
         <is>

--- a/output/台指期籌碼追蹤.xlsx
+++ b/output/台指期籌碼追蹤.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -137,12 +137,14 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3353,14 +3355,18 @@
       <c r="K54" s="22" t="n">
         <v>-3722.5</v>
       </c>
-      <c r="L54" s="20" t="inlineStr"/>
-      <c r="M54" s="19" t="inlineStr"/>
+      <c r="L54" s="21" t="n">
+        <v>-77</v>
+      </c>
+      <c r="M54" s="23" t="n">
+        <v>75600</v>
+      </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O54" s="23" t="inlineStr">
+      <c r="O54" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -3720,7 +3726,7 @@
       <c r="K61" s="11" t="n">
         <v>28274</v>
       </c>
-      <c r="L61" s="24" t="n">
+      <c r="L61" s="25" t="n">
         <v>-73</v>
       </c>
       <c r="M61" s="12" t="n">
@@ -3985,14 +3991,18 @@
       <c r="K66" s="22" t="n">
         <v>-55034.5</v>
       </c>
-      <c r="L66" s="20" t="inlineStr"/>
-      <c r="M66" s="19" t="inlineStr"/>
+      <c r="L66" s="22" t="n">
+        <v>-366</v>
+      </c>
+      <c r="M66" s="23" t="n">
+        <v>90050</v>
+      </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O66" s="23" t="inlineStr">
+      <c r="O66" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -5217,14 +5227,18 @@
       <c r="K90" s="22" t="n">
         <v>-27646.5</v>
       </c>
-      <c r="L90" s="20" t="inlineStr"/>
-      <c r="M90" s="19" t="inlineStr"/>
+      <c r="L90" s="21" t="n">
+        <v>-68</v>
+      </c>
+      <c r="M90" s="23" t="n">
+        <v>75150</v>
+      </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O90" s="23" t="inlineStr">
+      <c r="O90" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -5686,14 +5700,18 @@
       <c r="K99" s="22" t="n">
         <v>-41723</v>
       </c>
-      <c r="L99" s="20" t="inlineStr"/>
-      <c r="M99" s="19" t="inlineStr"/>
+      <c r="L99" s="22" t="n">
+        <v>-669</v>
+      </c>
+      <c r="M99" s="23" t="n">
+        <v>105200</v>
+      </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O99" s="23" t="inlineStr">
+      <c r="O99" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -6185,17 +6203,21 @@
       <c r="J109" s="21" t="n">
         <v>-10921.5</v>
       </c>
-      <c r="K109" s="25" t="n">
+      <c r="K109" s="26" t="n">
         <v>7775.5</v>
       </c>
-      <c r="L109" s="20" t="inlineStr"/>
-      <c r="M109" s="19" t="inlineStr"/>
+      <c r="L109" s="21" t="n">
+        <v>-34</v>
+      </c>
+      <c r="M109" s="23" t="n">
+        <v>73450</v>
+      </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O109" s="23" t="inlineStr">
+      <c r="O109" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -6445,14 +6467,18 @@
       <c r="K114" s="22" t="n">
         <v>-23902</v>
       </c>
-      <c r="L114" s="20" t="inlineStr"/>
-      <c r="M114" s="19" t="inlineStr"/>
+      <c r="L114" s="22" t="n">
+        <v>-632</v>
+      </c>
+      <c r="M114" s="23" t="n">
+        <v>103350</v>
+      </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O114" s="23" t="inlineStr">
+      <c r="O114" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -7089,7 +7115,7 @@
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O127" s="26" t="inlineStr">
+      <c r="O127" s="27" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
@@ -11950,7 +11976,7 @@
       <c r="I223" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J223" s="27" t="n">
+      <c r="J223" s="28" t="n">
         <v>0</v>
       </c>
       <c r="K223" s="7" t="n">
@@ -12473,7 +12499,7 @@
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O233" s="26" t="inlineStr">
+      <c r="O233" s="27" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
@@ -13804,14 +13830,18 @@
       <c r="K259" s="22" t="n">
         <v>-23662</v>
       </c>
-      <c r="L259" s="20" t="inlineStr"/>
-      <c r="M259" s="19" t="inlineStr"/>
+      <c r="L259" s="22" t="n">
+        <v>-324</v>
+      </c>
+      <c r="M259" s="23" t="n">
+        <v>87950</v>
+      </c>
       <c r="N259" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O259" s="23" t="inlineStr">
+      <c r="O259" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -15562,14 +15592,18 @@
       <c r="K293" s="22" t="n">
         <v>-27276</v>
       </c>
-      <c r="L293" s="20" t="inlineStr"/>
-      <c r="M293" s="19" t="inlineStr"/>
+      <c r="L293" s="22" t="n">
+        <v>-468</v>
+      </c>
+      <c r="M293" s="23" t="n">
+        <v>95150</v>
+      </c>
       <c r="N293" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O293" s="23" t="inlineStr">
+      <c r="O293" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -17148,7 +17182,7 @@
       <c r="L322" s="6" t="n">
         <v>-983</v>
       </c>
-      <c r="M322" s="28" t="n">
+      <c r="M322" s="29" t="n">
         <v>120900</v>
       </c>
       <c r="N322" s="2" t="inlineStr">
@@ -17805,7 +17839,7 @@
       <c r="K334" s="18" t="n">
         <v>-30169.5</v>
       </c>
-      <c r="L334" s="24" t="n">
+      <c r="L334" s="25" t="n">
         <v>-43</v>
       </c>
       <c r="M334" s="12" t="n">
@@ -17970,14 +18004,18 @@
       <c r="K337" s="22" t="n">
         <v>-9682</v>
       </c>
-      <c r="L337" s="20" t="inlineStr"/>
-      <c r="M337" s="19" t="inlineStr"/>
+      <c r="L337" s="22" t="n">
+        <v>-878</v>
+      </c>
+      <c r="M337" s="23" t="n">
+        <v>115650</v>
+      </c>
       <c r="N337" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O337" s="23" t="inlineStr">
+      <c r="O337" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -18241,7 +18279,7 @@
       <c r="K342" s="11" t="n">
         <v>16455</v>
       </c>
-      <c r="L342" s="24" t="n">
+      <c r="L342" s="25" t="n">
         <v>-14</v>
       </c>
       <c r="M342" s="12" t="n">
@@ -18626,7 +18664,7 @@
       <c r="K349" s="18" t="n">
         <v>-8530.5</v>
       </c>
-      <c r="L349" s="24" t="n">
+      <c r="L349" s="25" t="n">
         <v>-241</v>
       </c>
       <c r="M349" s="12" t="n">
@@ -19451,7 +19489,7 @@
       <c r="K364" s="11" t="n">
         <v>13916</v>
       </c>
-      <c r="L364" s="24" t="n">
+      <c r="L364" s="25" t="n">
         <v>-31</v>
       </c>
       <c r="M364" s="12" t="n">
@@ -20386,14 +20424,18 @@
       <c r="K381" s="22" t="n">
         <v>-30962.5</v>
       </c>
-      <c r="L381" s="20" t="inlineStr"/>
-      <c r="M381" s="19" t="inlineStr"/>
+      <c r="L381" s="22" t="n">
+        <v>-676</v>
+      </c>
+      <c r="M381" s="23" t="n">
+        <v>105550</v>
+      </c>
       <c r="N381" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O381" s="23" t="inlineStr">
+      <c r="O381" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -20712,14 +20754,18 @@
       <c r="K387" s="22" t="n">
         <v>-31528</v>
       </c>
-      <c r="L387" s="20" t="inlineStr"/>
-      <c r="M387" s="19" t="inlineStr"/>
+      <c r="L387" s="22" t="n">
+        <v>-455</v>
+      </c>
+      <c r="M387" s="23" t="n">
+        <v>94500</v>
+      </c>
       <c r="N387" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O387" s="23" t="inlineStr">
+      <c r="O387" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -21741,14 +21787,18 @@
       <c r="K406" s="22" t="n">
         <v>-42705.5</v>
       </c>
-      <c r="L406" s="20" t="inlineStr"/>
-      <c r="M406" s="19" t="inlineStr"/>
+      <c r="L406" s="22" t="n">
+        <v>-604</v>
+      </c>
+      <c r="M406" s="23" t="n">
+        <v>101950</v>
+      </c>
       <c r="N406" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O406" s="23" t="inlineStr">
+      <c r="O406" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -22095,7 +22145,7 @@
       <c r="J413" s="21" t="n">
         <v>-16971</v>
       </c>
-      <c r="K413" s="25" t="n">
+      <c r="K413" s="26" t="n">
         <v>4109.5</v>
       </c>
       <c r="L413" s="20" t="inlineStr"/>
@@ -22105,7 +22155,7 @@
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O413" s="26" t="inlineStr">
+      <c r="O413" s="27" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
@@ -22412,7 +22462,7 @@
       <c r="K419" s="11" t="n">
         <v>50393.5</v>
       </c>
-      <c r="L419" s="24" t="n">
+      <c r="L419" s="25" t="n">
         <v>-39</v>
       </c>
       <c r="M419" s="12" t="n">
@@ -23017,14 +23067,18 @@
       <c r="K430" s="22" t="n">
         <v>-52975</v>
       </c>
-      <c r="L430" s="20" t="inlineStr"/>
-      <c r="M430" s="19" t="inlineStr"/>
+      <c r="L430" s="22" t="n">
+        <v>-626</v>
+      </c>
+      <c r="M430" s="23" t="n">
+        <v>103050</v>
+      </c>
       <c r="N430" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O430" s="23" t="inlineStr">
+      <c r="O430" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -24044,7 +24098,7 @@
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O450" s="26" t="inlineStr">
+      <c r="O450" s="27" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
@@ -25293,7 +25347,7 @@
       <c r="K474" s="11" t="n">
         <v>1614.5</v>
       </c>
-      <c r="L474" s="24" t="n">
+      <c r="L474" s="25" t="n">
         <v>-159</v>
       </c>
       <c r="M474" s="12" t="n">
@@ -25568,14 +25622,18 @@
       <c r="K479" s="22" t="n">
         <v>-24654</v>
       </c>
-      <c r="L479" s="20" t="inlineStr"/>
-      <c r="M479" s="19" t="inlineStr"/>
+      <c r="L479" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M479" s="23" t="n">
+        <v>71750</v>
+      </c>
       <c r="N479" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O479" s="23" t="inlineStr">
+      <c r="O479" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -26220,14 +26278,18 @@
       <c r="K491" s="22" t="n">
         <v>-38717</v>
       </c>
-      <c r="L491" s="20" t="inlineStr"/>
-      <c r="M491" s="19" t="inlineStr"/>
+      <c r="L491" s="22" t="n">
+        <v>-1317</v>
+      </c>
+      <c r="M491" s="30" t="n">
+        <v>137600</v>
+      </c>
       <c r="N491" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O491" s="23" t="inlineStr">
+      <c r="O491" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -26914,7 +26976,7 @@
       <c r="L504" s="6" t="n">
         <v>-1279</v>
       </c>
-      <c r="M504" s="28" t="n">
+      <c r="M504" s="29" t="n">
         <v>135700</v>
       </c>
       <c r="N504" s="2" t="inlineStr">
@@ -26966,14 +27028,18 @@
       <c r="K505" s="22" t="n">
         <v>-84673</v>
       </c>
-      <c r="L505" s="20" t="inlineStr"/>
-      <c r="M505" s="19" t="inlineStr"/>
+      <c r="L505" s="22" t="n">
+        <v>-2770</v>
+      </c>
+      <c r="M505" s="30" t="n">
+        <v>210250</v>
+      </c>
       <c r="N505" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O505" s="23" t="inlineStr">
+      <c r="O505" s="24" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -27707,7 +27773,7 @@
       <c r="I2" s="3" t="n">
         <v>268336</v>
       </c>
-      <c r="J2" s="29" t="n">
+      <c r="J2" s="31" t="n">
         <v>78.90000000000001</v>
       </c>
       <c r="K2" s="16" t="inlineStr">
@@ -27748,7 +27814,7 @@
       <c r="I3" s="3" t="n">
         <v>270222</v>
       </c>
-      <c r="J3" s="29" t="n">
+      <c r="J3" s="31" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="K3" s="16" t="inlineStr">
@@ -27789,7 +27855,7 @@
       <c r="I4" s="3" t="n">
         <v>310408</v>
       </c>
-      <c r="J4" s="29" t="n">
+      <c r="J4" s="31" t="n">
         <v>106.9</v>
       </c>
       <c r="K4" s="16" t="inlineStr">
@@ -27830,10 +27896,10 @@
       <c r="I5" s="3" t="n">
         <v>302244</v>
       </c>
-      <c r="J5" s="29" t="n">
+      <c r="J5" s="31" t="n">
         <v>101.5</v>
       </c>
-      <c r="K5" s="30" t="inlineStr">
+      <c r="K5" s="32" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
@@ -27871,7 +27937,7 @@
       <c r="I6" s="3" t="n">
         <v>323030</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="31" t="n">
         <v>115.4</v>
       </c>
       <c r="K6" s="16" t="inlineStr">
@@ -27912,10 +27978,10 @@
       <c r="I7" s="3" t="n">
         <v>295666</v>
       </c>
-      <c r="J7" s="29" t="n">
+      <c r="J7" s="31" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="K7" s="30" t="inlineStr">
+      <c r="K7" s="32" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
@@ -27953,10 +28019,10 @@
       <c r="I8" s="3" t="n">
         <v>286802</v>
       </c>
-      <c r="J8" s="29" t="n">
+      <c r="J8" s="31" t="n">
         <v>91.2</v>
       </c>
-      <c r="K8" s="30" t="inlineStr">
+      <c r="K8" s="32" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
@@ -27994,7 +28060,7 @@
       <c r="I9" s="3" t="n">
         <v>326038</v>
       </c>
-      <c r="J9" s="29" t="n">
+      <c r="J9" s="31" t="n">
         <v>117.4</v>
       </c>
       <c r="K9" s="16" t="inlineStr">
@@ -28035,7 +28101,7 @@
       <c r="I10" s="3" t="n">
         <v>432624</v>
       </c>
-      <c r="J10" s="29" t="n">
+      <c r="J10" s="31" t="n">
         <v>188.4</v>
       </c>
       <c r="K10" s="16" t="inlineStr">
@@ -28076,7 +28142,7 @@
       <c r="I11" s="3" t="n">
         <v>531610</v>
       </c>
-      <c r="J11" s="29" t="n">
+      <c r="J11" s="31" t="n">
         <v>254.4</v>
       </c>
       <c r="K11" s="16" t="inlineStr">
@@ -28117,10 +28183,10 @@
       <c r="I12" s="3" t="n">
         <v>528496</v>
       </c>
-      <c r="J12" s="29" t="n">
+      <c r="J12" s="31" t="n">
         <v>252.3</v>
       </c>
-      <c r="K12" s="30" t="inlineStr">
+      <c r="K12" s="32" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
@@ -28158,7 +28224,7 @@
       <c r="I13" s="3" t="n">
         <v>588982</v>
       </c>
-      <c r="J13" s="29" t="n">
+      <c r="J13" s="31" t="n">
         <v>292.7</v>
       </c>
       <c r="K13" s="16" t="inlineStr">
@@ -28199,7 +28265,7 @@
       <c r="I14" s="3" t="n">
         <v>626818</v>
       </c>
-      <c r="J14" s="29" t="n">
+      <c r="J14" s="31" t="n">
         <v>317.9</v>
       </c>
       <c r="K14" s="16" t="inlineStr">
@@ -28240,7 +28306,7 @@
       <c r="I15" s="3" t="n">
         <v>758354</v>
       </c>
-      <c r="J15" s="29" t="n">
+      <c r="J15" s="31" t="n">
         <v>405.6</v>
       </c>
       <c r="K15" s="16" t="inlineStr">
@@ -28281,7 +28347,7 @@
       <c r="I16" s="3" t="n">
         <v>803490</v>
       </c>
-      <c r="J16" s="29" t="n">
+      <c r="J16" s="31" t="n">
         <v>435.7</v>
       </c>
       <c r="K16" s="16" t="inlineStr">
@@ -28322,7 +28388,7 @@
       <c r="I17" s="3" t="n">
         <v>831476</v>
       </c>
-      <c r="J17" s="29" t="n">
+      <c r="J17" s="31" t="n">
         <v>454.3</v>
       </c>
       <c r="K17" s="16" t="inlineStr">
@@ -28332,31 +28398,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>16筆</t>
         </is>
       </c>
-      <c r="E18" s="31" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>勝率75.0%</t>
         </is>
       </c>
-      <c r="F18" s="32" t="n">
+      <c r="F18" s="34" t="n">
         <v>13666</v>
       </c>
-      <c r="G18" s="32" t="n">
+      <c r="G18" s="34" t="n">
         <v>681476</v>
       </c>
-      <c r="I18" s="32" t="n">
+      <c r="I18" s="34" t="n">
         <v>831476</v>
       </c>
-      <c r="J18" s="33" t="n">
+      <c r="J18" s="35" t="n">
         <v>454.3</v>
       </c>
     </row>
@@ -29025,72 +29091,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="34" t="inlineStr">
+      <c r="B1" s="36" t="inlineStr">
         <is>
           <t>近月_ours</t>
         </is>
       </c>
-      <c r="C1" s="34" t="inlineStr">
+      <c r="C1" s="36" t="inlineStr">
         <is>
           <t>近月_correct</t>
         </is>
       </c>
-      <c r="D1" s="34" t="inlineStr">
+      <c r="D1" s="36" t="inlineStr">
         <is>
           <t>近月_diff</t>
         </is>
       </c>
-      <c r="E1" s="34" t="inlineStr">
+      <c r="E1" s="36" t="inlineStr">
         <is>
           <t>遠月_ours</t>
         </is>
       </c>
-      <c r="F1" s="34" t="inlineStr">
+      <c r="F1" s="36" t="inlineStr">
         <is>
           <t>遠月_correct</t>
         </is>
       </c>
-      <c r="G1" s="34" t="inlineStr">
+      <c r="G1" s="36" t="inlineStr">
         <is>
           <t>遠月_diff</t>
         </is>
       </c>
-      <c r="H1" s="34" t="inlineStr">
+      <c r="H1" s="36" t="inlineStr">
         <is>
           <t>小散戶_ours</t>
         </is>
       </c>
-      <c r="I1" s="34" t="inlineStr">
+      <c r="I1" s="36" t="inlineStr">
         <is>
           <t>小散戶_correct</t>
         </is>
       </c>
-      <c r="J1" s="34" t="inlineStr">
+      <c r="J1" s="36" t="inlineStr">
         <is>
           <t>小散戶_diff</t>
         </is>
       </c>
-      <c r="K1" s="34" t="inlineStr">
+      <c r="K1" s="36" t="inlineStr">
         <is>
           <t>主力_ours</t>
         </is>
       </c>
-      <c r="L1" s="34" t="inlineStr">
+      <c r="L1" s="36" t="inlineStr">
         <is>
           <t>主力_correct</t>
         </is>
       </c>
-      <c r="M1" s="34" t="inlineStr">
+      <c r="M1" s="36" t="inlineStr">
         <is>
           <t>主力_diff</t>
         </is>
       </c>
-      <c r="N1" s="34" t="inlineStr">
+      <c r="N1" s="36" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
@@ -29306,7 +29372,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>台指期籌碼策略（v2 優化版）</t>
         </is>
@@ -29316,7 +29382,7 @@
       <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>【資料來源】100% 期交所</t>
         </is>
@@ -29347,7 +29413,7 @@
       <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>【公式】</t>
         </is>
@@ -29392,7 +29458,7 @@
       <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>【策略（v2 優化版）】</t>
         </is>
@@ -29423,7 +29489,7 @@
       <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="A20" s="38" t="inlineStr">
         <is>
           <t>【信號說明】</t>
         </is>
@@ -29482,7 +29548,7 @@
       <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t>【操作欄說明】</t>
         </is>
@@ -29530,7 +29596,7 @@
       <c r="A36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="36" t="inlineStr">
+      <c r="A37" s="38" t="inlineStr">
         <is>
           <t>【改善原因】</t>
         </is>
@@ -29554,7 +29620,7 @@
       <c r="A40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="36" t="inlineStr">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>【成本】</t>
         </is>

--- a/output/台指期籌碼追蹤.xlsx
+++ b/output/台指期籌碼追蹤.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -137,14 +137,12 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -596,7 +594,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>最大回落</t>
+          <t>未實現損益</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1341,8 +1339,8 @@
       <c r="K16" s="7" t="n">
         <v>41736.5</v>
       </c>
-      <c r="L16" s="3" t="n">
-        <v>0</v>
+      <c r="L16" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="M16" s="15" t="n">
         <v>71750</v>
@@ -1394,8 +1392,8 @@
       <c r="K17" s="11" t="n">
         <v>70057</v>
       </c>
-      <c r="L17" s="9" t="n">
-        <v>0</v>
+      <c r="L17" s="10" t="n">
+        <v>54</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>71750</v>
@@ -1447,8 +1445,8 @@
       <c r="K18" s="7" t="n">
         <v>77159.5</v>
       </c>
-      <c r="L18" s="3" t="n">
-        <v>0</v>
+      <c r="L18" s="14" t="n">
+        <v>87</v>
       </c>
       <c r="M18" s="15" t="n">
         <v>71750</v>
@@ -1500,8 +1498,8 @@
       <c r="K19" s="7" t="n">
         <v>82988</v>
       </c>
-      <c r="L19" s="3" t="n">
-        <v>0</v>
+      <c r="L19" s="14" t="n">
+        <v>179</v>
       </c>
       <c r="M19" s="15" t="n">
         <v>71750</v>
@@ -1553,8 +1551,8 @@
       <c r="K20" s="7" t="n">
         <v>21630.5</v>
       </c>
-      <c r="L20" s="3" t="n">
-        <v>0</v>
+      <c r="L20" s="14" t="n">
+        <v>183</v>
       </c>
       <c r="M20" s="15" t="n">
         <v>71750</v>
@@ -1606,8 +1604,8 @@
       <c r="K21" s="7" t="n">
         <v>53556</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>0</v>
+      <c r="L21" s="14" t="n">
+        <v>309</v>
       </c>
       <c r="M21" s="15" t="n">
         <v>71750</v>
@@ -1659,11 +1657,11 @@
       <c r="K22" s="7" t="n">
         <v>8751</v>
       </c>
-      <c r="L22" s="4" t="n">
-        <v>-44</v>
+      <c r="L22" s="14" t="n">
+        <v>265</v>
       </c>
       <c r="M22" s="15" t="n">
-        <v>73950</v>
+        <v>71750</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1712,11 +1710,11 @@
       <c r="K23" s="6" t="n">
         <v>-20122.5</v>
       </c>
-      <c r="L23" s="4" t="n">
-        <v>-205</v>
+      <c r="L23" s="14" t="n">
+        <v>104</v>
       </c>
       <c r="M23" s="15" t="n">
-        <v>82000</v>
+        <v>71750</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1765,11 +1763,11 @@
       <c r="K24" s="6" t="n">
         <v>-31615.5</v>
       </c>
-      <c r="L24" s="4" t="n">
-        <v>-139</v>
+      <c r="L24" s="14" t="n">
+        <v>170</v>
       </c>
       <c r="M24" s="15" t="n">
-        <v>78700</v>
+        <v>71750</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1818,11 +1816,11 @@
       <c r="K25" s="6" t="n">
         <v>-29576</v>
       </c>
-      <c r="L25" s="4" t="n">
-        <v>-41</v>
+      <c r="L25" s="14" t="n">
+        <v>268</v>
       </c>
       <c r="M25" s="15" t="n">
-        <v>73800</v>
+        <v>71750</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1871,11 +1869,11 @@
       <c r="K26" s="6" t="n">
         <v>-44997.5</v>
       </c>
-      <c r="L26" s="4" t="n">
-        <v>-39</v>
+      <c r="L26" s="14" t="n">
+        <v>270</v>
       </c>
       <c r="M26" s="15" t="n">
-        <v>73700</v>
+        <v>71750</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1924,8 +1922,8 @@
       <c r="K27" s="6" t="n">
         <v>-503</v>
       </c>
-      <c r="L27" s="3" t="n">
-        <v>0</v>
+      <c r="L27" s="14" t="n">
+        <v>851</v>
       </c>
       <c r="M27" s="15" t="n">
         <v>71750</v>
@@ -1977,11 +1975,11 @@
       <c r="K28" s="7" t="n">
         <v>12951</v>
       </c>
-      <c r="L28" s="4" t="n">
-        <v>-33</v>
+      <c r="L28" s="14" t="n">
+        <v>818</v>
       </c>
       <c r="M28" s="15" t="n">
-        <v>73400</v>
+        <v>71750</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -2030,8 +2028,8 @@
       <c r="K29" s="7" t="n">
         <v>23101</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>0</v>
+      <c r="L29" s="14" t="n">
+        <v>855</v>
       </c>
       <c r="M29" s="15" t="n">
         <v>71750</v>
@@ -2083,8 +2081,8 @@
       <c r="K30" s="7" t="n">
         <v>41925</v>
       </c>
-      <c r="L30" s="3" t="n">
-        <v>0</v>
+      <c r="L30" s="14" t="n">
+        <v>937</v>
       </c>
       <c r="M30" s="15" t="n">
         <v>71750</v>
@@ -2136,11 +2134,11 @@
       <c r="K31" s="6" t="n">
         <v>-5167</v>
       </c>
-      <c r="L31" s="4" t="n">
-        <v>-83</v>
+      <c r="L31" s="14" t="n">
+        <v>854</v>
       </c>
       <c r="M31" s="15" t="n">
-        <v>75900</v>
+        <v>71750</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -2189,8 +2187,8 @@
       <c r="K32" s="6" t="n">
         <v>-11915.5</v>
       </c>
-      <c r="L32" s="3" t="n">
-        <v>0</v>
+      <c r="L32" s="14" t="n">
+        <v>1073</v>
       </c>
       <c r="M32" s="15" t="n">
         <v>71750</v>
@@ -2242,8 +2240,8 @@
       <c r="K33" s="6" t="n">
         <v>-9270.5</v>
       </c>
-      <c r="L33" s="3" t="n">
-        <v>0</v>
+      <c r="L33" s="14" t="n">
+        <v>1097</v>
       </c>
       <c r="M33" s="15" t="n">
         <v>71750</v>
@@ -2295,8 +2293,8 @@
       <c r="K34" s="6" t="n">
         <v>-7149</v>
       </c>
-      <c r="L34" s="3" t="n">
-        <v>0</v>
+      <c r="L34" s="14" t="n">
+        <v>1147</v>
       </c>
       <c r="M34" s="15" t="n">
         <v>71750</v>
@@ -2348,11 +2346,11 @@
       <c r="K35" s="6" t="n">
         <v>-48310.5</v>
       </c>
-      <c r="L35" s="4" t="n">
-        <v>-96</v>
+      <c r="L35" s="14" t="n">
+        <v>1051</v>
       </c>
       <c r="M35" s="15" t="n">
-        <v>76550</v>
+        <v>71750</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2401,8 +2399,8 @@
       <c r="K36" s="7" t="n">
         <v>13443.5</v>
       </c>
-      <c r="L36" s="3" t="n">
-        <v>0</v>
+      <c r="L36" s="14" t="n">
+        <v>1150</v>
       </c>
       <c r="M36" s="15" t="n">
         <v>71750</v>
@@ -2454,11 +2452,11 @@
       <c r="K37" s="6" t="n">
         <v>-14964</v>
       </c>
-      <c r="L37" s="4" t="n">
-        <v>-5</v>
+      <c r="L37" s="14" t="n">
+        <v>1145</v>
       </c>
       <c r="M37" s="15" t="n">
-        <v>72000</v>
+        <v>71750</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2507,8 +2505,8 @@
       <c r="K38" s="7" t="n">
         <v>36875</v>
       </c>
-      <c r="L38" s="3" t="n">
-        <v>0</v>
+      <c r="L38" s="14" t="n">
+        <v>1498</v>
       </c>
       <c r="M38" s="15" t="n">
         <v>71750</v>
@@ -2560,8 +2558,8 @@
       <c r="K39" s="7" t="n">
         <v>3285</v>
       </c>
-      <c r="L39" s="3" t="n">
-        <v>0</v>
+      <c r="L39" s="14" t="n">
+        <v>1573</v>
       </c>
       <c r="M39" s="15" t="n">
         <v>71750</v>
@@ -2613,8 +2611,8 @@
       <c r="K40" s="7" t="n">
         <v>33728.5</v>
       </c>
-      <c r="L40" s="3" t="n">
-        <v>0</v>
+      <c r="L40" s="14" t="n">
+        <v>1693</v>
       </c>
       <c r="M40" s="15" t="n">
         <v>71750</v>
@@ -2666,8 +2664,8 @@
       <c r="K41" s="7" t="n">
         <v>9739</v>
       </c>
-      <c r="L41" s="3" t="n">
-        <v>0</v>
+      <c r="L41" s="14" t="n">
+        <v>1893</v>
       </c>
       <c r="M41" s="15" t="n">
         <v>71750</v>
@@ -2719,8 +2717,8 @@
       <c r="K42" s="6" t="n">
         <v>-392</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>0</v>
+      <c r="L42" s="14" t="n">
+        <v>1975</v>
       </c>
       <c r="M42" s="15" t="n">
         <v>71750</v>
@@ -2772,11 +2770,11 @@
       <c r="K43" s="6" t="n">
         <v>-47495</v>
       </c>
-      <c r="L43" s="4" t="n">
-        <v>-76</v>
+      <c r="L43" s="14" t="n">
+        <v>1899</v>
       </c>
       <c r="M43" s="15" t="n">
-        <v>75550</v>
+        <v>71750</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2825,8 +2823,8 @@
       <c r="K44" s="18" t="n">
         <v>-15698</v>
       </c>
-      <c r="L44" s="9" t="n">
-        <v>0</v>
+      <c r="L44" s="10" t="n">
+        <v>2139</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>71750</v>
@@ -2878,11 +2876,11 @@
       <c r="K45" s="6" t="n">
         <v>-33181.5</v>
       </c>
-      <c r="L45" s="4" t="n">
-        <v>-28</v>
+      <c r="L45" s="14" t="n">
+        <v>2111</v>
       </c>
       <c r="M45" s="15" t="n">
-        <v>73150</v>
+        <v>71750</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2931,11 +2929,11 @@
       <c r="K46" s="6" t="n">
         <v>-23316</v>
       </c>
-      <c r="L46" s="4" t="n">
-        <v>-16</v>
+      <c r="L46" s="14" t="n">
+        <v>2123</v>
       </c>
       <c r="M46" s="15" t="n">
-        <v>72550</v>
+        <v>71750</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2984,11 +2982,11 @@
       <c r="K47" s="6" t="n">
         <v>-21190.5</v>
       </c>
-      <c r="L47" s="4" t="n">
-        <v>-225</v>
+      <c r="L47" s="14" t="n">
+        <v>1914</v>
       </c>
       <c r="M47" s="15" t="n">
-        <v>83000</v>
+        <v>71750</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -3037,11 +3035,11 @@
       <c r="K48" s="7" t="n">
         <v>1931.5</v>
       </c>
-      <c r="L48" s="4" t="n">
-        <v>-36</v>
+      <c r="L48" s="14" t="n">
+        <v>2103</v>
       </c>
       <c r="M48" s="15" t="n">
-        <v>73550</v>
+        <v>71750</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -3090,11 +3088,11 @@
       <c r="K49" s="6" t="n">
         <v>-18625.5</v>
       </c>
-      <c r="L49" s="4" t="n">
-        <v>-88</v>
+      <c r="L49" s="14" t="n">
+        <v>2051</v>
       </c>
       <c r="M49" s="15" t="n">
-        <v>76150</v>
+        <v>71750</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -3143,11 +3141,11 @@
       <c r="K50" s="6" t="n">
         <v>-11145</v>
       </c>
-      <c r="L50" s="4" t="n">
-        <v>-208</v>
+      <c r="L50" s="14" t="n">
+        <v>1931</v>
       </c>
       <c r="M50" s="15" t="n">
-        <v>82150</v>
+        <v>71750</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -3196,8 +3194,8 @@
       <c r="K51" s="11" t="n">
         <v>24580</v>
       </c>
-      <c r="L51" s="9" t="n">
-        <v>0</v>
+      <c r="L51" s="10" t="n">
+        <v>2448</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>71750</v>
@@ -3249,11 +3247,11 @@
       <c r="K52" s="7" t="n">
         <v>10934.5</v>
       </c>
-      <c r="L52" s="4" t="n">
-        <v>-22</v>
+      <c r="L52" s="14" t="n">
+        <v>2426</v>
       </c>
       <c r="M52" s="15" t="n">
-        <v>72850</v>
+        <v>71750</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3302,11 +3300,11 @@
       <c r="K53" s="6" t="n">
         <v>-6517.5</v>
       </c>
-      <c r="L53" s="4" t="n">
-        <v>-33</v>
+      <c r="L53" s="14" t="n">
+        <v>2415</v>
       </c>
       <c r="M53" s="15" t="n">
-        <v>73400</v>
+        <v>71750</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3355,18 +3353,18 @@
       <c r="K54" s="22" t="n">
         <v>-3722.5</v>
       </c>
-      <c r="L54" s="21" t="n">
-        <v>-77</v>
-      </c>
-      <c r="M54" s="23" t="n">
-        <v>75600</v>
+      <c r="L54" s="23" t="n">
+        <v>2371</v>
+      </c>
+      <c r="M54" s="24" t="n">
+        <v>71750</v>
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O54" s="24" t="inlineStr">
+      <c r="O54" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -3462,10 +3460,10 @@
         <v>-42203</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>-58</v>
+        <v>-35</v>
       </c>
       <c r="M56" s="15" t="n">
-        <v>74650</v>
+        <v>73500</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3514,8 +3512,8 @@
       <c r="K57" s="11" t="n">
         <v>15833.5</v>
       </c>
-      <c r="L57" s="9" t="n">
-        <v>0</v>
+      <c r="L57" s="10" t="n">
+        <v>42</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>71750</v>
@@ -3567,8 +3565,8 @@
       <c r="K58" s="7" t="n">
         <v>6133.5</v>
       </c>
-      <c r="L58" s="3" t="n">
-        <v>0</v>
+      <c r="L58" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="M58" s="15" t="n">
         <v>71750</v>
@@ -3620,8 +3618,8 @@
       <c r="K59" s="11" t="n">
         <v>51542</v>
       </c>
-      <c r="L59" s="9" t="n">
-        <v>0</v>
+      <c r="L59" s="10" t="n">
+        <v>285</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>71750</v>
@@ -3673,11 +3671,11 @@
       <c r="K60" s="6" t="n">
         <v>-8405</v>
       </c>
-      <c r="L60" s="4" t="n">
-        <v>-174</v>
+      <c r="L60" s="14" t="n">
+        <v>111</v>
       </c>
       <c r="M60" s="15" t="n">
-        <v>80450</v>
+        <v>71750</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3726,11 +3724,11 @@
       <c r="K61" s="11" t="n">
         <v>28274</v>
       </c>
-      <c r="L61" s="25" t="n">
-        <v>-73</v>
+      <c r="L61" s="10" t="n">
+        <v>212</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>75400</v>
+        <v>71750</v>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
@@ -3779,8 +3777,8 @@
       <c r="K62" s="7" t="n">
         <v>42397</v>
       </c>
-      <c r="L62" s="3" t="n">
-        <v>0</v>
+      <c r="L62" s="14" t="n">
+        <v>636</v>
       </c>
       <c r="M62" s="15" t="n">
         <v>71750</v>
@@ -3832,11 +3830,11 @@
       <c r="K63" s="7" t="n">
         <v>19531.5</v>
       </c>
-      <c r="L63" s="4" t="n">
-        <v>-23</v>
+      <c r="L63" s="14" t="n">
+        <v>613</v>
       </c>
       <c r="M63" s="15" t="n">
-        <v>72900</v>
+        <v>71750</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3885,11 +3883,11 @@
       <c r="K64" s="6" t="n">
         <v>-50899.5</v>
       </c>
-      <c r="L64" s="4" t="n">
-        <v>-121</v>
+      <c r="L64" s="14" t="n">
+        <v>515</v>
       </c>
       <c r="M64" s="15" t="n">
-        <v>77800</v>
+        <v>71750</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3938,11 +3936,11 @@
       <c r="K65" s="6" t="n">
         <v>-2868</v>
       </c>
-      <c r="L65" s="4" t="n">
-        <v>-119</v>
+      <c r="L65" s="14" t="n">
+        <v>517</v>
       </c>
       <c r="M65" s="15" t="n">
-        <v>77700</v>
+        <v>71750</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -3991,18 +3989,18 @@
       <c r="K66" s="22" t="n">
         <v>-55034.5</v>
       </c>
-      <c r="L66" s="22" t="n">
-        <v>-366</v>
-      </c>
-      <c r="M66" s="23" t="n">
-        <v>90050</v>
+      <c r="L66" s="23" t="n">
+        <v>270</v>
+      </c>
+      <c r="M66" s="24" t="n">
+        <v>71750</v>
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O66" s="24" t="inlineStr">
+      <c r="O66" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -4539,10 +4537,10 @@
         <v>27687</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>-139</v>
+        <v>-105</v>
       </c>
       <c r="M77" s="15" t="n">
-        <v>78700</v>
+        <v>77000</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -4592,10 +4590,10 @@
         <v>-17827</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>-261</v>
+        <v>-227</v>
       </c>
       <c r="M78" s="15" t="n">
-        <v>84800</v>
+        <v>83100</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
@@ -4645,10 +4643,10 @@
         <v>13996</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>-170</v>
+        <v>-136</v>
       </c>
       <c r="M79" s="15" t="n">
-        <v>80250</v>
+        <v>78550</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4697,8 +4695,8 @@
       <c r="K80" s="6" t="n">
         <v>-3953</v>
       </c>
-      <c r="L80" s="3" t="n">
-        <v>0</v>
+      <c r="L80" s="14" t="n">
+        <v>84</v>
       </c>
       <c r="M80" s="15" t="n">
         <v>71750</v>
@@ -4750,8 +4748,8 @@
       <c r="K81" s="6" t="n">
         <v>-17598</v>
       </c>
-      <c r="L81" s="3" t="n">
-        <v>0</v>
+      <c r="L81" s="14" t="n">
+        <v>132</v>
       </c>
       <c r="M81" s="15" t="n">
         <v>71750</v>
@@ -4803,8 +4801,8 @@
       <c r="K82" s="11" t="n">
         <v>7886</v>
       </c>
-      <c r="L82" s="9" t="n">
-        <v>0</v>
+      <c r="L82" s="10" t="n">
+        <v>207</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>71750</v>
@@ -4856,11 +4854,11 @@
       <c r="K83" s="7" t="n">
         <v>9471</v>
       </c>
-      <c r="L83" s="4" t="n">
-        <v>-113</v>
+      <c r="L83" s="14" t="n">
+        <v>94</v>
       </c>
       <c r="M83" s="15" t="n">
-        <v>77400</v>
+        <v>71750</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -4909,8 +4907,8 @@
       <c r="K84" s="11" t="n">
         <v>45294.5</v>
       </c>
-      <c r="L84" s="9" t="n">
-        <v>0</v>
+      <c r="L84" s="10" t="n">
+        <v>291</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>71750</v>
@@ -4962,8 +4960,8 @@
       <c r="K85" s="7" t="n">
         <v>5285</v>
       </c>
-      <c r="L85" s="3" t="n">
-        <v>0</v>
+      <c r="L85" s="14" t="n">
+        <v>365</v>
       </c>
       <c r="M85" s="15" t="n">
         <v>71750</v>
@@ -5015,8 +5013,8 @@
       <c r="K86" s="7" t="n">
         <v>26351.5</v>
       </c>
-      <c r="L86" s="3" t="n">
-        <v>0</v>
+      <c r="L86" s="14" t="n">
+        <v>495</v>
       </c>
       <c r="M86" s="15" t="n">
         <v>71750</v>
@@ -5068,8 +5066,8 @@
       <c r="K87" s="7" t="n">
         <v>3763</v>
       </c>
-      <c r="L87" s="3" t="n">
-        <v>0</v>
+      <c r="L87" s="14" t="n">
+        <v>625</v>
       </c>
       <c r="M87" s="15" t="n">
         <v>71750</v>
@@ -5121,8 +5119,8 @@
       <c r="K88" s="7" t="n">
         <v>1146</v>
       </c>
-      <c r="L88" s="3" t="n">
-        <v>0</v>
+      <c r="L88" s="14" t="n">
+        <v>852</v>
       </c>
       <c r="M88" s="15" t="n">
         <v>71750</v>
@@ -5174,11 +5172,11 @@
       <c r="K89" s="6" t="n">
         <v>-38262</v>
       </c>
-      <c r="L89" s="4" t="n">
-        <v>-34</v>
+      <c r="L89" s="14" t="n">
+        <v>818</v>
       </c>
       <c r="M89" s="15" t="n">
-        <v>73450</v>
+        <v>71750</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
@@ -5227,18 +5225,18 @@
       <c r="K90" s="22" t="n">
         <v>-27646.5</v>
       </c>
-      <c r="L90" s="21" t="n">
-        <v>-68</v>
-      </c>
-      <c r="M90" s="23" t="n">
-        <v>75150</v>
+      <c r="L90" s="23" t="n">
+        <v>784</v>
+      </c>
+      <c r="M90" s="24" t="n">
+        <v>71750</v>
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O90" s="24" t="inlineStr">
+      <c r="O90" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -5382,11 +5380,11 @@
       <c r="K93" s="7" t="n">
         <v>5377.5</v>
       </c>
-      <c r="L93" s="3" t="n">
-        <v>0</v>
+      <c r="L93" s="4" t="n">
+        <v>-26</v>
       </c>
       <c r="M93" s="15" t="n">
-        <v>71750</v>
+        <v>73050</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
@@ -5436,10 +5434,10 @@
         <v>7607</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>-39</v>
+        <v>-65</v>
       </c>
       <c r="M94" s="15" t="n">
-        <v>73700</v>
+        <v>75000</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
@@ -5488,8 +5486,8 @@
       <c r="K95" s="7" t="n">
         <v>25382</v>
       </c>
-      <c r="L95" s="3" t="n">
-        <v>0</v>
+      <c r="L95" s="14" t="n">
+        <v>245</v>
       </c>
       <c r="M95" s="15" t="n">
         <v>71750</v>
@@ -5541,8 +5539,8 @@
       <c r="K96" s="7" t="n">
         <v>17532</v>
       </c>
-      <c r="L96" s="3" t="n">
-        <v>0</v>
+      <c r="L96" s="14" t="n">
+        <v>324</v>
       </c>
       <c r="M96" s="15" t="n">
         <v>71750</v>
@@ -5594,11 +5592,11 @@
       <c r="K97" s="6" t="n">
         <v>-53324</v>
       </c>
-      <c r="L97" s="4" t="n">
-        <v>-232</v>
+      <c r="L97" s="14" t="n">
+        <v>92</v>
       </c>
       <c r="M97" s="15" t="n">
-        <v>83350</v>
+        <v>71750</v>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
@@ -5647,11 +5645,11 @@
       <c r="K98" s="6" t="n">
         <v>-45262</v>
       </c>
-      <c r="L98" s="6" t="n">
-        <v>-563</v>
+      <c r="L98" s="4" t="n">
+        <v>-239</v>
       </c>
       <c r="M98" s="15" t="n">
-        <v>99900</v>
+        <v>83700</v>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
@@ -5701,17 +5699,17 @@
         <v>-41723</v>
       </c>
       <c r="L99" s="22" t="n">
-        <v>-669</v>
-      </c>
-      <c r="M99" s="23" t="n">
-        <v>105200</v>
+        <v>-345</v>
+      </c>
+      <c r="M99" s="24" t="n">
+        <v>89000</v>
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O99" s="24" t="inlineStr">
+      <c r="O99" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -6100,8 +6098,8 @@
       <c r="K107" s="7" t="n">
         <v>37078</v>
       </c>
-      <c r="L107" s="3" t="n">
-        <v>0</v>
+      <c r="L107" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="M107" s="15" t="n">
         <v>71750</v>
@@ -6153,8 +6151,8 @@
       <c r="K108" s="7" t="n">
         <v>8124.5</v>
       </c>
-      <c r="L108" s="3" t="n">
-        <v>0</v>
+      <c r="L108" s="14" t="n">
+        <v>203</v>
       </c>
       <c r="M108" s="15" t="n">
         <v>71750</v>
@@ -6206,18 +6204,18 @@
       <c r="K109" s="26" t="n">
         <v>7775.5</v>
       </c>
-      <c r="L109" s="21" t="n">
-        <v>-34</v>
-      </c>
-      <c r="M109" s="23" t="n">
-        <v>73450</v>
+      <c r="L109" s="23" t="n">
+        <v>169</v>
+      </c>
+      <c r="M109" s="24" t="n">
+        <v>71750</v>
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O109" s="24" t="inlineStr">
+      <c r="O109" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -6361,8 +6359,8 @@
       <c r="K112" s="6" t="n">
         <v>-1108</v>
       </c>
-      <c r="L112" s="3" t="n">
-        <v>0</v>
+      <c r="L112" s="14" t="n">
+        <v>225</v>
       </c>
       <c r="M112" s="15" t="n">
         <v>71750</v>
@@ -6414,11 +6412,11 @@
       <c r="K113" s="6" t="n">
         <v>-17823</v>
       </c>
-      <c r="L113" s="4" t="n">
-        <v>-168</v>
+      <c r="L113" s="14" t="n">
+        <v>57</v>
       </c>
       <c r="M113" s="15" t="n">
-        <v>80150</v>
+        <v>71750</v>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
@@ -6468,17 +6466,17 @@
         <v>-23902</v>
       </c>
       <c r="L114" s="22" t="n">
-        <v>-632</v>
-      </c>
-      <c r="M114" s="23" t="n">
-        <v>103350</v>
+        <v>-407</v>
+      </c>
+      <c r="M114" s="24" t="n">
+        <v>92100</v>
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O114" s="24" t="inlineStr">
+      <c r="O114" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -13720,11 +13718,11 @@
       <c r="K257" s="6" t="n">
         <v>-1694.5</v>
       </c>
-      <c r="L257" s="4" t="n">
-        <v>-187</v>
+      <c r="L257" s="14" t="n">
+        <v>9</v>
       </c>
       <c r="M257" s="15" t="n">
-        <v>81100</v>
+        <v>71750</v>
       </c>
       <c r="N257" s="2" t="inlineStr">
         <is>
@@ -13775,11 +13773,11 @@
       <c r="K258" s="6" t="n">
         <v>-18449.5</v>
       </c>
-      <c r="L258" s="6" t="n">
-        <v>-446</v>
+      <c r="L258" s="4" t="n">
+        <v>-250</v>
       </c>
       <c r="M258" s="15" t="n">
-        <v>94050</v>
+        <v>84250</v>
       </c>
       <c r="N258" s="2" t="inlineStr">
         <is>
@@ -13830,18 +13828,18 @@
       <c r="K259" s="22" t="n">
         <v>-23662</v>
       </c>
-      <c r="L259" s="22" t="n">
-        <v>-324</v>
-      </c>
-      <c r="M259" s="23" t="n">
-        <v>87950</v>
+      <c r="L259" s="21" t="n">
+        <v>-128</v>
+      </c>
+      <c r="M259" s="24" t="n">
+        <v>78150</v>
       </c>
       <c r="N259" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O259" s="24" t="inlineStr">
+      <c r="O259" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -15317,8 +15315,8 @@
       <c r="K288" s="7" t="n">
         <v>25857.5</v>
       </c>
-      <c r="L288" s="3" t="n">
-        <v>0</v>
+      <c r="L288" s="14" t="n">
+        <v>964</v>
       </c>
       <c r="M288" s="15" t="n">
         <v>71750</v>
@@ -15372,11 +15370,11 @@
       <c r="K289" s="7" t="n">
         <v>11431</v>
       </c>
-      <c r="L289" s="4" t="n">
-        <v>-33</v>
+      <c r="L289" s="14" t="n">
+        <v>931</v>
       </c>
       <c r="M289" s="15" t="n">
-        <v>73400</v>
+        <v>71750</v>
       </c>
       <c r="N289" s="2" t="inlineStr">
         <is>
@@ -15427,8 +15425,8 @@
       <c r="K290" s="7" t="n">
         <v>41251</v>
       </c>
-      <c r="L290" s="3" t="n">
-        <v>0</v>
+      <c r="L290" s="14" t="n">
+        <v>1238</v>
       </c>
       <c r="M290" s="15" t="n">
         <v>71750</v>
@@ -15482,11 +15480,11 @@
       <c r="K291" s="7" t="n">
         <v>21660.5</v>
       </c>
-      <c r="L291" s="4" t="n">
-        <v>-250</v>
+      <c r="L291" s="14" t="n">
+        <v>988</v>
       </c>
       <c r="M291" s="15" t="n">
-        <v>84250</v>
+        <v>71750</v>
       </c>
       <c r="N291" s="2" t="inlineStr">
         <is>
@@ -15537,11 +15535,11 @@
       <c r="K292" s="6" t="n">
         <v>-13219</v>
       </c>
-      <c r="L292" s="6" t="n">
-        <v>-429</v>
+      <c r="L292" s="14" t="n">
+        <v>809</v>
       </c>
       <c r="M292" s="15" t="n">
-        <v>93200</v>
+        <v>71750</v>
       </c>
       <c r="N292" s="2" t="inlineStr">
         <is>
@@ -15592,18 +15590,18 @@
       <c r="K293" s="22" t="n">
         <v>-27276</v>
       </c>
-      <c r="L293" s="22" t="n">
-        <v>-468</v>
-      </c>
-      <c r="M293" s="23" t="n">
-        <v>95150</v>
+      <c r="L293" s="23" t="n">
+        <v>770</v>
+      </c>
+      <c r="M293" s="24" t="n">
+        <v>71750</v>
       </c>
       <c r="N293" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O293" s="24" t="inlineStr">
+      <c r="O293" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -15805,10 +15803,10 @@
         <v>13991.5</v>
       </c>
       <c r="L297" s="4" t="n">
-        <v>-88</v>
+        <v>-170</v>
       </c>
       <c r="M297" s="15" t="n">
-        <v>76150</v>
+        <v>80250</v>
       </c>
       <c r="N297" s="2" t="inlineStr">
         <is>
@@ -15859,8 +15857,8 @@
       <c r="K298" s="7" t="n">
         <v>32997</v>
       </c>
-      <c r="L298" s="3" t="n">
-        <v>0</v>
+      <c r="L298" s="14" t="n">
+        <v>237</v>
       </c>
       <c r="M298" s="15" t="n">
         <v>71750</v>
@@ -15914,8 +15912,8 @@
       <c r="K299" s="7" t="n">
         <v>30861</v>
       </c>
-      <c r="L299" s="3" t="n">
-        <v>0</v>
+      <c r="L299" s="14" t="n">
+        <v>329</v>
       </c>
       <c r="M299" s="15" t="n">
         <v>71750</v>
@@ -15969,8 +15967,8 @@
       <c r="K300" s="7" t="n">
         <v>42566.5</v>
       </c>
-      <c r="L300" s="3" t="n">
-        <v>0</v>
+      <c r="L300" s="14" t="n">
+        <v>518</v>
       </c>
       <c r="M300" s="15" t="n">
         <v>71750</v>
@@ -16024,11 +16022,11 @@
       <c r="K301" s="7" t="n">
         <v>10694</v>
       </c>
-      <c r="L301" s="4" t="n">
-        <v>-5</v>
+      <c r="L301" s="14" t="n">
+        <v>513</v>
       </c>
       <c r="M301" s="15" t="n">
-        <v>72000</v>
+        <v>71750</v>
       </c>
       <c r="N301" s="2" t="inlineStr">
         <is>
@@ -16079,8 +16077,8 @@
       <c r="K302" s="7" t="n">
         <v>37927</v>
       </c>
-      <c r="L302" s="3" t="n">
-        <v>0</v>
+      <c r="L302" s="14" t="n">
+        <v>1041</v>
       </c>
       <c r="M302" s="15" t="n">
         <v>71750</v>
@@ -16134,11 +16132,11 @@
       <c r="K303" s="6" t="n">
         <v>-16487</v>
       </c>
-      <c r="L303" s="4" t="n">
-        <v>-273</v>
+      <c r="L303" s="14" t="n">
+        <v>768</v>
       </c>
       <c r="M303" s="15" t="n">
-        <v>85400</v>
+        <v>71750</v>
       </c>
       <c r="N303" s="2" t="inlineStr">
         <is>
@@ -16189,11 +16187,11 @@
       <c r="K304" s="6" t="n">
         <v>-7720.5</v>
       </c>
-      <c r="L304" s="6" t="n">
-        <v>-340</v>
+      <c r="L304" s="14" t="n">
+        <v>701</v>
       </c>
       <c r="M304" s="15" t="n">
-        <v>88750</v>
+        <v>71750</v>
       </c>
       <c r="N304" s="2" t="inlineStr">
         <is>
@@ -16244,11 +16242,11 @@
       <c r="K305" s="6" t="n">
         <v>-8281.5</v>
       </c>
-      <c r="L305" s="4" t="n">
-        <v>-296</v>
+      <c r="L305" s="14" t="n">
+        <v>745</v>
       </c>
       <c r="M305" s="15" t="n">
-        <v>86550</v>
+        <v>71750</v>
       </c>
       <c r="N305" s="2" t="inlineStr">
         <is>
@@ -16299,11 +16297,11 @@
       <c r="K306" s="6" t="n">
         <v>-4028</v>
       </c>
-      <c r="L306" s="4" t="n">
-        <v>-102</v>
+      <c r="L306" s="14" t="n">
+        <v>939</v>
       </c>
       <c r="M306" s="15" t="n">
-        <v>76850</v>
+        <v>71750</v>
       </c>
       <c r="N306" s="2" t="inlineStr">
         <is>
@@ -16354,8 +16352,8 @@
       <c r="K307" s="6" t="n">
         <v>-15209.5</v>
       </c>
-      <c r="L307" s="3" t="n">
-        <v>0</v>
+      <c r="L307" s="14" t="n">
+        <v>1212</v>
       </c>
       <c r="M307" s="15" t="n">
         <v>71750</v>
@@ -16409,8 +16407,8 @@
       <c r="K308" s="7" t="n">
         <v>11429</v>
       </c>
-      <c r="L308" s="3" t="n">
-        <v>0</v>
+      <c r="L308" s="14" t="n">
+        <v>1430</v>
       </c>
       <c r="M308" s="15" t="n">
         <v>71750</v>
@@ -16464,8 +16462,8 @@
       <c r="K309" s="7" t="n">
         <v>18825</v>
       </c>
-      <c r="L309" s="3" t="n">
-        <v>0</v>
+      <c r="L309" s="14" t="n">
+        <v>1724</v>
       </c>
       <c r="M309" s="15" t="n">
         <v>71750</v>
@@ -16519,8 +16517,8 @@
       <c r="K310" s="7" t="n">
         <v>34389</v>
       </c>
-      <c r="L310" s="3" t="n">
-        <v>0</v>
+      <c r="L310" s="14" t="n">
+        <v>2132</v>
       </c>
       <c r="M310" s="15" t="n">
         <v>71750</v>
@@ -16574,11 +16572,11 @@
       <c r="K311" s="7" t="n">
         <v>17643.5</v>
       </c>
-      <c r="L311" s="4" t="n">
-        <v>-74</v>
+      <c r="L311" s="14" t="n">
+        <v>2058</v>
       </c>
       <c r="M311" s="15" t="n">
-        <v>75450</v>
+        <v>71750</v>
       </c>
       <c r="N311" s="2" t="inlineStr">
         <is>
@@ -16629,8 +16627,8 @@
       <c r="K312" s="7" t="n">
         <v>8617.5</v>
       </c>
-      <c r="L312" s="3" t="n">
-        <v>0</v>
+      <c r="L312" s="14" t="n">
+        <v>2185</v>
       </c>
       <c r="M312" s="15" t="n">
         <v>71750</v>
@@ -16684,11 +16682,11 @@
       <c r="K313" s="7" t="n">
         <v>2234</v>
       </c>
-      <c r="L313" s="4" t="n">
-        <v>-283</v>
+      <c r="L313" s="14" t="n">
+        <v>1902</v>
       </c>
       <c r="M313" s="15" t="n">
-        <v>85900</v>
+        <v>71750</v>
       </c>
       <c r="N313" s="2" t="inlineStr">
         <is>
@@ -16739,11 +16737,11 @@
       <c r="K314" s="6" t="n">
         <v>-11592.5</v>
       </c>
-      <c r="L314" s="4" t="n">
-        <v>-282</v>
+      <c r="L314" s="14" t="n">
+        <v>1903</v>
       </c>
       <c r="M314" s="15" t="n">
-        <v>85850</v>
+        <v>71750</v>
       </c>
       <c r="N314" s="2" t="inlineStr">
         <is>
@@ -16794,8 +16792,8 @@
       <c r="K315" s="6" t="n">
         <v>-19734.5</v>
       </c>
-      <c r="L315" s="3" t="n">
-        <v>0</v>
+      <c r="L315" s="14" t="n">
+        <v>2213</v>
       </c>
       <c r="M315" s="15" t="n">
         <v>71750</v>
@@ -16849,11 +16847,11 @@
       <c r="K316" s="6" t="n">
         <v>-36283</v>
       </c>
-      <c r="L316" s="6" t="n">
-        <v>-346</v>
+      <c r="L316" s="14" t="n">
+        <v>1867</v>
       </c>
       <c r="M316" s="15" t="n">
-        <v>89050</v>
+        <v>71750</v>
       </c>
       <c r="N316" s="2" t="inlineStr">
         <is>
@@ -16904,11 +16902,11 @@
       <c r="K317" s="6" t="n">
         <v>-33684</v>
       </c>
-      <c r="L317" s="6" t="n">
-        <v>-379</v>
+      <c r="L317" s="14" t="n">
+        <v>1834</v>
       </c>
       <c r="M317" s="15" t="n">
-        <v>90700</v>
+        <v>71750</v>
       </c>
       <c r="N317" s="2" t="inlineStr">
         <is>
@@ -16959,11 +16957,11 @@
       <c r="K318" s="6" t="n">
         <v>-21112</v>
       </c>
-      <c r="L318" s="6" t="n">
-        <v>-464</v>
+      <c r="L318" s="14" t="n">
+        <v>1749</v>
       </c>
       <c r="M318" s="15" t="n">
-        <v>94950</v>
+        <v>71750</v>
       </c>
       <c r="N318" s="2" t="inlineStr">
         <is>
@@ -17014,11 +17012,11 @@
       <c r="K319" s="6" t="n">
         <v>-31270</v>
       </c>
-      <c r="L319" s="6" t="n">
-        <v>-616</v>
+      <c r="L319" s="14" t="n">
+        <v>1597</v>
       </c>
       <c r="M319" s="15" t="n">
-        <v>102550</v>
+        <v>71750</v>
       </c>
       <c r="N319" s="2" t="inlineStr">
         <is>
@@ -17069,11 +17067,11 @@
       <c r="K320" s="6" t="n">
         <v>-30092</v>
       </c>
-      <c r="L320" s="6" t="n">
-        <v>-597</v>
+      <c r="L320" s="14" t="n">
+        <v>1616</v>
       </c>
       <c r="M320" s="15" t="n">
-        <v>101600</v>
+        <v>71750</v>
       </c>
       <c r="N320" s="2" t="inlineStr">
         <is>
@@ -17124,11 +17122,11 @@
       <c r="K321" s="6" t="n">
         <v>-26255</v>
       </c>
-      <c r="L321" s="6" t="n">
-        <v>-529</v>
+      <c r="L321" s="14" t="n">
+        <v>1684</v>
       </c>
       <c r="M321" s="15" t="n">
-        <v>98200</v>
+        <v>71750</v>
       </c>
       <c r="N321" s="2" t="inlineStr">
         <is>
@@ -17179,11 +17177,11 @@
       <c r="K322" s="6" t="n">
         <v>-34648.5</v>
       </c>
-      <c r="L322" s="6" t="n">
-        <v>-983</v>
-      </c>
-      <c r="M322" s="29" t="n">
-        <v>120900</v>
+      <c r="L322" s="14" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M322" s="15" t="n">
+        <v>71750</v>
       </c>
       <c r="N322" s="2" t="inlineStr">
         <is>
@@ -17234,11 +17232,11 @@
       <c r="K323" s="11" t="n">
         <v>1246</v>
       </c>
-      <c r="L323" s="18" t="n">
-        <v>-878</v>
+      <c r="L323" s="10" t="n">
+        <v>1335</v>
       </c>
       <c r="M323" s="12" t="n">
-        <v>115650</v>
+        <v>71750</v>
       </c>
       <c r="N323" s="8" t="inlineStr">
         <is>
@@ -17289,11 +17287,11 @@
       <c r="K324" s="7" t="n">
         <v>40964.5</v>
       </c>
-      <c r="L324" s="6" t="n">
-        <v>-367</v>
+      <c r="L324" s="14" t="n">
+        <v>1846</v>
       </c>
       <c r="M324" s="15" t="n">
-        <v>90100</v>
+        <v>71750</v>
       </c>
       <c r="N324" s="2" t="inlineStr">
         <is>
@@ -17344,11 +17342,11 @@
       <c r="K325" s="7" t="n">
         <v>27915.5</v>
       </c>
-      <c r="L325" s="4" t="n">
-        <v>-296</v>
+      <c r="L325" s="14" t="n">
+        <v>1917</v>
       </c>
       <c r="M325" s="15" t="n">
-        <v>86550</v>
+        <v>71750</v>
       </c>
       <c r="N325" s="2" t="inlineStr">
         <is>
@@ -17399,11 +17397,11 @@
       <c r="K326" s="7" t="n">
         <v>35193.5</v>
       </c>
-      <c r="L326" s="4" t="n">
-        <v>-271</v>
+      <c r="L326" s="14" t="n">
+        <v>1942</v>
       </c>
       <c r="M326" s="15" t="n">
-        <v>85300</v>
+        <v>71750</v>
       </c>
       <c r="N326" s="2" t="inlineStr">
         <is>
@@ -17454,11 +17452,11 @@
       <c r="K327" s="7" t="n">
         <v>44451.5</v>
       </c>
-      <c r="L327" s="4" t="n">
-        <v>-122</v>
+      <c r="L327" s="14" t="n">
+        <v>2091</v>
       </c>
       <c r="M327" s="15" t="n">
-        <v>77850</v>
+        <v>71750</v>
       </c>
       <c r="N327" s="2" t="inlineStr">
         <is>
@@ -17509,8 +17507,8 @@
       <c r="K328" s="7" t="n">
         <v>27513</v>
       </c>
-      <c r="L328" s="3" t="n">
-        <v>0</v>
+      <c r="L328" s="14" t="n">
+        <v>2477</v>
       </c>
       <c r="M328" s="15" t="n">
         <v>71750</v>
@@ -17564,8 +17562,8 @@
       <c r="K329" s="7" t="n">
         <v>6783.5</v>
       </c>
-      <c r="L329" s="3" t="n">
-        <v>0</v>
+      <c r="L329" s="14" t="n">
+        <v>2715</v>
       </c>
       <c r="M329" s="15" t="n">
         <v>71750</v>
@@ -17619,11 +17617,11 @@
       <c r="K330" s="6" t="n">
         <v>-6289</v>
       </c>
-      <c r="L330" s="4" t="n">
-        <v>-99</v>
+      <c r="L330" s="14" t="n">
+        <v>2616</v>
       </c>
       <c r="M330" s="15" t="n">
-        <v>76700</v>
+        <v>71750</v>
       </c>
       <c r="N330" s="2" t="inlineStr">
         <is>
@@ -17674,11 +17672,11 @@
       <c r="K331" s="6" t="n">
         <v>-15211</v>
       </c>
-      <c r="L331" s="6" t="n">
-        <v>-411</v>
+      <c r="L331" s="14" t="n">
+        <v>2304</v>
       </c>
       <c r="M331" s="15" t="n">
-        <v>92300</v>
+        <v>71750</v>
       </c>
       <c r="N331" s="2" t="inlineStr">
         <is>
@@ -17729,11 +17727,11 @@
       <c r="K332" s="6" t="n">
         <v>-16265</v>
       </c>
-      <c r="L332" s="6" t="n">
-        <v>-319</v>
+      <c r="L332" s="14" t="n">
+        <v>2396</v>
       </c>
       <c r="M332" s="15" t="n">
-        <v>87700</v>
+        <v>71750</v>
       </c>
       <c r="N332" s="2" t="inlineStr">
         <is>
@@ -17784,11 +17782,11 @@
       <c r="K333" s="6" t="n">
         <v>-32011.5</v>
       </c>
-      <c r="L333" s="4" t="n">
-        <v>-192</v>
+      <c r="L333" s="14" t="n">
+        <v>2523</v>
       </c>
       <c r="M333" s="15" t="n">
-        <v>81350</v>
+        <v>71750</v>
       </c>
       <c r="N333" s="2" t="inlineStr">
         <is>
@@ -17839,11 +17837,11 @@
       <c r="K334" s="18" t="n">
         <v>-30169.5</v>
       </c>
-      <c r="L334" s="25" t="n">
-        <v>-43</v>
+      <c r="L334" s="10" t="n">
+        <v>2672</v>
       </c>
       <c r="M334" s="12" t="n">
-        <v>73900</v>
+        <v>71750</v>
       </c>
       <c r="N334" s="8" t="inlineStr">
         <is>
@@ -17894,11 +17892,11 @@
       <c r="K335" s="6" t="n">
         <v>-31385</v>
       </c>
-      <c r="L335" s="6" t="n">
-        <v>-647</v>
+      <c r="L335" s="14" t="n">
+        <v>2068</v>
       </c>
       <c r="M335" s="15" t="n">
-        <v>104100</v>
+        <v>71750</v>
       </c>
       <c r="N335" s="2" t="inlineStr">
         <is>
@@ -17949,11 +17947,11 @@
       <c r="K336" s="6" t="n">
         <v>-7640</v>
       </c>
-      <c r="L336" s="6" t="n">
-        <v>-698</v>
+      <c r="L336" s="14" t="n">
+        <v>2017</v>
       </c>
       <c r="M336" s="15" t="n">
-        <v>106650</v>
+        <v>71750</v>
       </c>
       <c r="N336" s="2" t="inlineStr">
         <is>
@@ -18004,18 +18002,18 @@
       <c r="K337" s="22" t="n">
         <v>-9682</v>
       </c>
-      <c r="L337" s="22" t="n">
-        <v>-878</v>
-      </c>
-      <c r="M337" s="23" t="n">
-        <v>115650</v>
+      <c r="L337" s="23" t="n">
+        <v>1837</v>
+      </c>
+      <c r="M337" s="24" t="n">
+        <v>71750</v>
       </c>
       <c r="N337" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O337" s="24" t="inlineStr">
+      <c r="O337" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -18114,8 +18112,8 @@
       <c r="K339" s="7" t="n">
         <v>2715</v>
       </c>
-      <c r="L339" s="3" t="n">
-        <v>0</v>
+      <c r="L339" s="14" t="n">
+        <v>21</v>
       </c>
       <c r="M339" s="15" t="n">
         <v>71750</v>
@@ -18170,10 +18168,10 @@
         <v>12201</v>
       </c>
       <c r="L340" s="4" t="n">
-        <v>-42</v>
+        <v>-21</v>
       </c>
       <c r="M340" s="15" t="n">
-        <v>73850</v>
+        <v>72800</v>
       </c>
       <c r="N340" s="2" t="inlineStr">
         <is>
@@ -18225,10 +18223,10 @@
         <v>-1228</v>
       </c>
       <c r="L341" s="4" t="n">
-        <v>-38</v>
+        <v>-17</v>
       </c>
       <c r="M341" s="15" t="n">
-        <v>73650</v>
+        <v>72600</v>
       </c>
       <c r="N341" s="2" t="inlineStr">
         <is>
@@ -18279,11 +18277,11 @@
       <c r="K342" s="11" t="n">
         <v>16455</v>
       </c>
-      <c r="L342" s="25" t="n">
-        <v>-14</v>
+      <c r="L342" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="M342" s="12" t="n">
-        <v>72450</v>
+        <v>71750</v>
       </c>
       <c r="N342" s="8" t="inlineStr">
         <is>
@@ -18334,8 +18332,8 @@
       <c r="K343" s="7" t="n">
         <v>3621</v>
       </c>
-      <c r="L343" s="3" t="n">
-        <v>0</v>
+      <c r="L343" s="14" t="n">
+        <v>215</v>
       </c>
       <c r="M343" s="15" t="n">
         <v>71750</v>
@@ -18389,8 +18387,8 @@
       <c r="K344" s="7" t="n">
         <v>10286</v>
       </c>
-      <c r="L344" s="3" t="n">
-        <v>0</v>
+      <c r="L344" s="14" t="n">
+        <v>258</v>
       </c>
       <c r="M344" s="15" t="n">
         <v>71750</v>
@@ -18444,8 +18442,8 @@
       <c r="K345" s="7" t="n">
         <v>39828</v>
       </c>
-      <c r="L345" s="3" t="n">
-        <v>0</v>
+      <c r="L345" s="14" t="n">
+        <v>537</v>
       </c>
       <c r="M345" s="15" t="n">
         <v>71750</v>
@@ -18499,11 +18497,11 @@
       <c r="K346" s="7" t="n">
         <v>16562.5</v>
       </c>
-      <c r="L346" s="4" t="n">
-        <v>-240</v>
+      <c r="L346" s="14" t="n">
+        <v>297</v>
       </c>
       <c r="M346" s="15" t="n">
-        <v>83750</v>
+        <v>71750</v>
       </c>
       <c r="N346" s="2" t="inlineStr">
         <is>
@@ -18554,11 +18552,11 @@
       <c r="K347" s="6" t="n">
         <v>-3358.5</v>
       </c>
-      <c r="L347" s="6" t="n">
-        <v>-339</v>
+      <c r="L347" s="14" t="n">
+        <v>198</v>
       </c>
       <c r="M347" s="15" t="n">
-        <v>88700</v>
+        <v>71750</v>
       </c>
       <c r="N347" s="2" t="inlineStr">
         <is>
@@ -18609,11 +18607,11 @@
       <c r="K348" s="6" t="n">
         <v>-21010.5</v>
       </c>
-      <c r="L348" s="6" t="n">
-        <v>-424</v>
+      <c r="L348" s="14" t="n">
+        <v>113</v>
       </c>
       <c r="M348" s="15" t="n">
-        <v>92950</v>
+        <v>71750</v>
       </c>
       <c r="N348" s="2" t="inlineStr">
         <is>
@@ -18664,11 +18662,11 @@
       <c r="K349" s="18" t="n">
         <v>-8530.5</v>
       </c>
-      <c r="L349" s="25" t="n">
-        <v>-241</v>
+      <c r="L349" s="10" t="n">
+        <v>296</v>
       </c>
       <c r="M349" s="12" t="n">
-        <v>83800</v>
+        <v>71750</v>
       </c>
       <c r="N349" s="8" t="inlineStr">
         <is>
@@ -18719,11 +18717,11 @@
       <c r="K350" s="6" t="n">
         <v>-15199.5</v>
       </c>
-      <c r="L350" s="4" t="n">
-        <v>-64</v>
+      <c r="L350" s="14" t="n">
+        <v>473</v>
       </c>
       <c r="M350" s="15" t="n">
-        <v>74950</v>
+        <v>71750</v>
       </c>
       <c r="N350" s="2" t="inlineStr">
         <is>
@@ -18774,8 +18772,8 @@
       <c r="K351" s="7" t="n">
         <v>26878.5</v>
       </c>
-      <c r="L351" s="3" t="n">
-        <v>0</v>
+      <c r="L351" s="14" t="n">
+        <v>626</v>
       </c>
       <c r="M351" s="15" t="n">
         <v>71750</v>
@@ -18829,11 +18827,11 @@
       <c r="K352" s="7" t="n">
         <v>9039.5</v>
       </c>
-      <c r="L352" s="4" t="n">
-        <v>-213</v>
+      <c r="L352" s="14" t="n">
+        <v>413</v>
       </c>
       <c r="M352" s="15" t="n">
-        <v>82400</v>
+        <v>71750</v>
       </c>
       <c r="N352" s="2" t="inlineStr">
         <is>
@@ -18884,8 +18882,8 @@
       <c r="K353" s="7" t="n">
         <v>39394.5</v>
       </c>
-      <c r="L353" s="3" t="n">
-        <v>0</v>
+      <c r="L353" s="14" t="n">
+        <v>672</v>
       </c>
       <c r="M353" s="15" t="n">
         <v>71750</v>
@@ -18939,8 +18937,8 @@
       <c r="K354" s="7" t="n">
         <v>28341.5</v>
       </c>
-      <c r="L354" s="3" t="n">
-        <v>0</v>
+      <c r="L354" s="14" t="n">
+        <v>909</v>
       </c>
       <c r="M354" s="15" t="n">
         <v>71750</v>
@@ -18994,8 +18992,8 @@
       <c r="K355" s="7" t="n">
         <v>8151</v>
       </c>
-      <c r="L355" s="3" t="n">
-        <v>0</v>
+      <c r="L355" s="14" t="n">
+        <v>1010</v>
       </c>
       <c r="M355" s="15" t="n">
         <v>71750</v>
@@ -19049,8 +19047,8 @@
       <c r="K356" s="6" t="n">
         <v>-13954.5</v>
       </c>
-      <c r="L356" s="3" t="n">
-        <v>0</v>
+      <c r="L356" s="14" t="n">
+        <v>1124</v>
       </c>
       <c r="M356" s="15" t="n">
         <v>71750</v>
@@ -19104,11 +19102,11 @@
       <c r="K357" s="7" t="n">
         <v>2740</v>
       </c>
-      <c r="L357" s="4" t="n">
-        <v>-34</v>
+      <c r="L357" s="14" t="n">
+        <v>1090</v>
       </c>
       <c r="M357" s="15" t="n">
-        <v>73450</v>
+        <v>71750</v>
       </c>
       <c r="N357" s="2" t="inlineStr">
         <is>
@@ -19159,11 +19157,11 @@
       <c r="K358" s="6" t="n">
         <v>-32557</v>
       </c>
-      <c r="L358" s="4" t="n">
-        <v>-272</v>
+      <c r="L358" s="14" t="n">
+        <v>852</v>
       </c>
       <c r="M358" s="15" t="n">
-        <v>85350</v>
+        <v>71750</v>
       </c>
       <c r="N358" s="2" t="inlineStr">
         <is>
@@ -19214,11 +19212,11 @@
       <c r="K359" s="6" t="n">
         <v>-26701</v>
       </c>
-      <c r="L359" s="4" t="n">
-        <v>-76</v>
+      <c r="L359" s="14" t="n">
+        <v>1048</v>
       </c>
       <c r="M359" s="15" t="n">
-        <v>75550</v>
+        <v>71750</v>
       </c>
       <c r="N359" s="2" t="inlineStr">
         <is>
@@ -19269,8 +19267,8 @@
       <c r="K360" s="6" t="n">
         <v>-25071.5</v>
       </c>
-      <c r="L360" s="3" t="n">
-        <v>0</v>
+      <c r="L360" s="14" t="n">
+        <v>1172</v>
       </c>
       <c r="M360" s="15" t="n">
         <v>71750</v>
@@ -19324,11 +19322,11 @@
       <c r="K361" s="6" t="n">
         <v>-23034.5</v>
       </c>
-      <c r="L361" s="4" t="n">
-        <v>-72</v>
+      <c r="L361" s="14" t="n">
+        <v>1100</v>
       </c>
       <c r="M361" s="15" t="n">
-        <v>75350</v>
+        <v>71750</v>
       </c>
       <c r="N361" s="2" t="inlineStr">
         <is>
@@ -19379,8 +19377,8 @@
       <c r="K362" s="18" t="n">
         <v>-11317</v>
       </c>
-      <c r="L362" s="9" t="n">
-        <v>0</v>
+      <c r="L362" s="10" t="n">
+        <v>1254</v>
       </c>
       <c r="M362" s="12" t="n">
         <v>71750</v>
@@ -19434,11 +19432,11 @@
       <c r="K363" s="6" t="n">
         <v>-3489.5</v>
       </c>
-      <c r="L363" s="4" t="n">
-        <v>-229</v>
+      <c r="L363" s="14" t="n">
+        <v>1025</v>
       </c>
       <c r="M363" s="15" t="n">
-        <v>83200</v>
+        <v>71750</v>
       </c>
       <c r="N363" s="2" t="inlineStr">
         <is>
@@ -19489,11 +19487,11 @@
       <c r="K364" s="11" t="n">
         <v>13916</v>
       </c>
-      <c r="L364" s="25" t="n">
-        <v>-31</v>
+      <c r="L364" s="10" t="n">
+        <v>1223</v>
       </c>
       <c r="M364" s="12" t="n">
-        <v>73300</v>
+        <v>71750</v>
       </c>
       <c r="N364" s="8" t="inlineStr">
         <is>
@@ -19544,8 +19542,8 @@
       <c r="K365" s="7" t="n">
         <v>26770</v>
       </c>
-      <c r="L365" s="3" t="n">
-        <v>0</v>
+      <c r="L365" s="14" t="n">
+        <v>1451</v>
       </c>
       <c r="M365" s="15" t="n">
         <v>71750</v>
@@ -19599,11 +19597,11 @@
       <c r="K366" s="7" t="n">
         <v>5467</v>
       </c>
-      <c r="L366" s="4" t="n">
-        <v>-245</v>
+      <c r="L366" s="14" t="n">
+        <v>1206</v>
       </c>
       <c r="M366" s="15" t="n">
-        <v>84000</v>
+        <v>71750</v>
       </c>
       <c r="N366" s="2" t="inlineStr">
         <is>
@@ -19654,11 +19652,11 @@
       <c r="K367" s="7" t="n">
         <v>3636.5</v>
       </c>
-      <c r="L367" s="6" t="n">
-        <v>-329</v>
+      <c r="L367" s="14" t="n">
+        <v>1122</v>
       </c>
       <c r="M367" s="15" t="n">
-        <v>88200</v>
+        <v>71750</v>
       </c>
       <c r="N367" s="2" t="inlineStr">
         <is>
@@ -19709,11 +19707,11 @@
       <c r="K368" s="7" t="n">
         <v>36302.5</v>
       </c>
-      <c r="L368" s="4" t="n">
-        <v>-14</v>
+      <c r="L368" s="14" t="n">
+        <v>1437</v>
       </c>
       <c r="M368" s="15" t="n">
-        <v>72450</v>
+        <v>71750</v>
       </c>
       <c r="N368" s="2" t="inlineStr">
         <is>
@@ -19764,11 +19762,11 @@
       <c r="K369" s="6" t="n">
         <v>-6431.5</v>
       </c>
-      <c r="L369" s="4" t="n">
-        <v>-164</v>
+      <c r="L369" s="14" t="n">
+        <v>1287</v>
       </c>
       <c r="M369" s="15" t="n">
-        <v>79950</v>
+        <v>71750</v>
       </c>
       <c r="N369" s="2" t="inlineStr">
         <is>
@@ -19819,8 +19817,8 @@
       <c r="K370" s="7" t="n">
         <v>14197.5</v>
       </c>
-      <c r="L370" s="3" t="n">
-        <v>0</v>
+      <c r="L370" s="14" t="n">
+        <v>1859</v>
       </c>
       <c r="M370" s="15" t="n">
         <v>71750</v>
@@ -19874,11 +19872,11 @@
       <c r="K371" s="7" t="n">
         <v>29188.5</v>
       </c>
-      <c r="L371" s="4" t="n">
-        <v>-48</v>
+      <c r="L371" s="14" t="n">
+        <v>1811</v>
       </c>
       <c r="M371" s="15" t="n">
-        <v>74150</v>
+        <v>71750</v>
       </c>
       <c r="N371" s="2" t="inlineStr">
         <is>
@@ -19929,8 +19927,8 @@
       <c r="K372" s="7" t="n">
         <v>28473</v>
       </c>
-      <c r="L372" s="3" t="n">
-        <v>0</v>
+      <c r="L372" s="14" t="n">
+        <v>2024</v>
       </c>
       <c r="M372" s="15" t="n">
         <v>71750</v>
@@ -19984,11 +19982,11 @@
       <c r="K373" s="6" t="n">
         <v>-919.5</v>
       </c>
-      <c r="L373" s="4" t="n">
-        <v>-27</v>
+      <c r="L373" s="14" t="n">
+        <v>1997</v>
       </c>
       <c r="M373" s="15" t="n">
-        <v>73100</v>
+        <v>71750</v>
       </c>
       <c r="N373" s="2" t="inlineStr">
         <is>
@@ -20039,8 +20037,8 @@
       <c r="K374" s="7" t="n">
         <v>18852</v>
       </c>
-      <c r="L374" s="3" t="n">
-        <v>0</v>
+      <c r="L374" s="14" t="n">
+        <v>2209</v>
       </c>
       <c r="M374" s="15" t="n">
         <v>71750</v>
@@ -20094,11 +20092,11 @@
       <c r="K375" s="6" t="n">
         <v>-21253.5</v>
       </c>
-      <c r="L375" s="4" t="n">
-        <v>-97</v>
+      <c r="L375" s="14" t="n">
+        <v>2112</v>
       </c>
       <c r="M375" s="15" t="n">
-        <v>76600</v>
+        <v>71750</v>
       </c>
       <c r="N375" s="2" t="inlineStr">
         <is>
@@ -20149,11 +20147,11 @@
       <c r="K376" s="6" t="n">
         <v>-12715</v>
       </c>
-      <c r="L376" s="4" t="n">
-        <v>-35</v>
+      <c r="L376" s="14" t="n">
+        <v>2174</v>
       </c>
       <c r="M376" s="15" t="n">
-        <v>73500</v>
+        <v>71750</v>
       </c>
       <c r="N376" s="2" t="inlineStr">
         <is>
@@ -20204,8 +20202,8 @@
       <c r="K377" s="6" t="n">
         <v>-269.5</v>
       </c>
-      <c r="L377" s="3" t="n">
-        <v>0</v>
+      <c r="L377" s="14" t="n">
+        <v>2288</v>
       </c>
       <c r="M377" s="15" t="n">
         <v>71750</v>
@@ -20259,11 +20257,11 @@
       <c r="K378" s="6" t="n">
         <v>-21688</v>
       </c>
-      <c r="L378" s="4" t="n">
-        <v>-84</v>
+      <c r="L378" s="14" t="n">
+        <v>2204</v>
       </c>
       <c r="M378" s="15" t="n">
-        <v>75950</v>
+        <v>71750</v>
       </c>
       <c r="N378" s="2" t="inlineStr">
         <is>
@@ -20314,11 +20312,11 @@
       <c r="K379" s="6" t="n">
         <v>-83374.5</v>
       </c>
-      <c r="L379" s="6" t="n">
-        <v>-789</v>
+      <c r="L379" s="14" t="n">
+        <v>1499</v>
       </c>
       <c r="M379" s="15" t="n">
-        <v>111200</v>
+        <v>71750</v>
       </c>
       <c r="N379" s="2" t="inlineStr">
         <is>
@@ -20369,11 +20367,11 @@
       <c r="K380" s="6" t="n">
         <v>-45677.5</v>
       </c>
-      <c r="L380" s="6" t="n">
-        <v>-574</v>
+      <c r="L380" s="14" t="n">
+        <v>1714</v>
       </c>
       <c r="M380" s="15" t="n">
-        <v>100450</v>
+        <v>71750</v>
       </c>
       <c r="N380" s="2" t="inlineStr">
         <is>
@@ -20424,18 +20422,18 @@
       <c r="K381" s="22" t="n">
         <v>-30962.5</v>
       </c>
-      <c r="L381" s="22" t="n">
-        <v>-676</v>
-      </c>
-      <c r="M381" s="23" t="n">
-        <v>105550</v>
+      <c r="L381" s="23" t="n">
+        <v>1612</v>
+      </c>
+      <c r="M381" s="24" t="n">
+        <v>71750</v>
       </c>
       <c r="N381" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O381" s="24" t="inlineStr">
+      <c r="O381" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -20534,8 +20532,8 @@
       <c r="K383" s="6" t="n">
         <v>-19142.5</v>
       </c>
-      <c r="L383" s="3" t="n">
-        <v>0</v>
+      <c r="L383" s="14" t="n">
+        <v>110</v>
       </c>
       <c r="M383" s="15" t="n">
         <v>71750</v>
@@ -20589,8 +20587,8 @@
       <c r="K384" s="11" t="n">
         <v>56167.5</v>
       </c>
-      <c r="L384" s="9" t="n">
-        <v>0</v>
+      <c r="L384" s="10" t="n">
+        <v>320</v>
       </c>
       <c r="M384" s="12" t="n">
         <v>71750</v>
@@ -20644,11 +20642,11 @@
       <c r="K385" s="7" t="n">
         <v>7156</v>
       </c>
-      <c r="L385" s="4" t="n">
-        <v>-235</v>
+      <c r="L385" s="14" t="n">
+        <v>85</v>
       </c>
       <c r="M385" s="15" t="n">
-        <v>83500</v>
+        <v>71750</v>
       </c>
       <c r="N385" s="2" t="inlineStr">
         <is>
@@ -20699,11 +20697,11 @@
       <c r="K386" s="7" t="n">
         <v>1688.5</v>
       </c>
-      <c r="L386" s="4" t="n">
-        <v>-196</v>
+      <c r="L386" s="14" t="n">
+        <v>124</v>
       </c>
       <c r="M386" s="15" t="n">
-        <v>81550</v>
+        <v>71750</v>
       </c>
       <c r="N386" s="2" t="inlineStr">
         <is>
@@ -20754,18 +20752,18 @@
       <c r="K387" s="22" t="n">
         <v>-31528</v>
       </c>
-      <c r="L387" s="22" t="n">
-        <v>-455</v>
-      </c>
-      <c r="M387" s="23" t="n">
-        <v>94500</v>
+      <c r="L387" s="21" t="n">
+        <v>-135</v>
+      </c>
+      <c r="M387" s="24" t="n">
+        <v>78500</v>
       </c>
       <c r="N387" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O387" s="24" t="inlineStr">
+      <c r="O387" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -21017,11 +21015,11 @@
       <c r="K392" s="7" t="n">
         <v>43189</v>
       </c>
-      <c r="L392" s="3" t="n">
-        <v>0</v>
+      <c r="L392" s="4" t="n">
+        <v>-37</v>
       </c>
       <c r="M392" s="15" t="n">
-        <v>71750</v>
+        <v>73600</v>
       </c>
       <c r="N392" s="2" t="inlineStr">
         <is>
@@ -21072,8 +21070,8 @@
       <c r="K393" s="7" t="n">
         <v>45646</v>
       </c>
-      <c r="L393" s="3" t="n">
-        <v>0</v>
+      <c r="L393" s="14" t="n">
+        <v>214</v>
       </c>
       <c r="M393" s="15" t="n">
         <v>71750</v>
@@ -21127,8 +21125,8 @@
       <c r="K394" s="7" t="n">
         <v>60788.5</v>
       </c>
-      <c r="L394" s="3" t="n">
-        <v>0</v>
+      <c r="L394" s="14" t="n">
+        <v>590</v>
       </c>
       <c r="M394" s="15" t="n">
         <v>71750</v>
@@ -21182,8 +21180,8 @@
       <c r="K395" s="7" t="n">
         <v>39286</v>
       </c>
-      <c r="L395" s="3" t="n">
-        <v>0</v>
+      <c r="L395" s="14" t="n">
+        <v>652</v>
       </c>
       <c r="M395" s="15" t="n">
         <v>71750</v>
@@ -21237,8 +21235,8 @@
       <c r="K396" s="7" t="n">
         <v>13401</v>
       </c>
-      <c r="L396" s="3" t="n">
-        <v>0</v>
+      <c r="L396" s="14" t="n">
+        <v>871</v>
       </c>
       <c r="M396" s="15" t="n">
         <v>71750</v>
@@ -21292,11 +21290,11 @@
       <c r="K397" s="7" t="n">
         <v>2091.5</v>
       </c>
-      <c r="L397" s="4" t="n">
-        <v>-106</v>
+      <c r="L397" s="14" t="n">
+        <v>765</v>
       </c>
       <c r="M397" s="15" t="n">
-        <v>77050</v>
+        <v>71750</v>
       </c>
       <c r="N397" s="2" t="inlineStr">
         <is>
@@ -21347,8 +21345,8 @@
       <c r="K398" s="6" t="n">
         <v>-1436.5</v>
       </c>
-      <c r="L398" s="3" t="n">
-        <v>0</v>
+      <c r="L398" s="14" t="n">
+        <v>1041</v>
       </c>
       <c r="M398" s="15" t="n">
         <v>71750</v>
@@ -21402,11 +21400,11 @@
       <c r="K399" s="6" t="n">
         <v>-40383.5</v>
       </c>
-      <c r="L399" s="4" t="n">
-        <v>-196</v>
+      <c r="L399" s="14" t="n">
+        <v>845</v>
       </c>
       <c r="M399" s="15" t="n">
-        <v>81550</v>
+        <v>71750</v>
       </c>
       <c r="N399" s="2" t="inlineStr">
         <is>
@@ -21457,8 +21455,8 @@
       <c r="K400" s="18" t="n">
         <v>-21529</v>
       </c>
-      <c r="L400" s="9" t="n">
-        <v>0</v>
+      <c r="L400" s="10" t="n">
+        <v>1121</v>
       </c>
       <c r="M400" s="12" t="n">
         <v>71750</v>
@@ -21512,11 +21510,11 @@
       <c r="K401" s="6" t="n">
         <v>-30246.5</v>
       </c>
-      <c r="L401" s="4" t="n">
-        <v>-38</v>
+      <c r="L401" s="14" t="n">
+        <v>1083</v>
       </c>
       <c r="M401" s="15" t="n">
-        <v>73650</v>
+        <v>71750</v>
       </c>
       <c r="N401" s="2" t="inlineStr">
         <is>
@@ -21567,8 +21565,8 @@
       <c r="K402" s="18" t="n">
         <v>-13658.5</v>
       </c>
-      <c r="L402" s="9" t="n">
-        <v>0</v>
+      <c r="L402" s="10" t="n">
+        <v>1303</v>
       </c>
       <c r="M402" s="12" t="n">
         <v>71750</v>
@@ -21622,8 +21620,8 @@
       <c r="K403" s="6" t="n">
         <v>-12163</v>
       </c>
-      <c r="L403" s="3" t="n">
-        <v>0</v>
+      <c r="L403" s="14" t="n">
+        <v>1685</v>
       </c>
       <c r="M403" s="15" t="n">
         <v>71750</v>
@@ -21677,11 +21675,11 @@
       <c r="K404" s="6" t="n">
         <v>-13197.5</v>
       </c>
-      <c r="L404" s="4" t="n">
-        <v>-36</v>
+      <c r="L404" s="14" t="n">
+        <v>1649</v>
       </c>
       <c r="M404" s="15" t="n">
-        <v>73550</v>
+        <v>71750</v>
       </c>
       <c r="N404" s="2" t="inlineStr">
         <is>
@@ -21732,11 +21730,11 @@
       <c r="K405" s="6" t="n">
         <v>-22845.5</v>
       </c>
-      <c r="L405" s="4" t="n">
-        <v>-176</v>
+      <c r="L405" s="14" t="n">
+        <v>1509</v>
       </c>
       <c r="M405" s="15" t="n">
-        <v>80550</v>
+        <v>71750</v>
       </c>
       <c r="N405" s="2" t="inlineStr">
         <is>
@@ -21787,18 +21785,18 @@
       <c r="K406" s="22" t="n">
         <v>-42705.5</v>
       </c>
-      <c r="L406" s="22" t="n">
-        <v>-604</v>
-      </c>
-      <c r="M406" s="23" t="n">
-        <v>101950</v>
+      <c r="L406" s="23" t="n">
+        <v>1081</v>
+      </c>
+      <c r="M406" s="24" t="n">
+        <v>71750</v>
       </c>
       <c r="N406" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O406" s="24" t="inlineStr">
+      <c r="O406" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -22407,11 +22405,11 @@
       <c r="K418" s="7" t="n">
         <v>4706</v>
       </c>
-      <c r="L418" s="6" t="n">
-        <v>-494</v>
+      <c r="L418" s="14" t="n">
+        <v>77</v>
       </c>
       <c r="M418" s="15" t="n">
-        <v>96450</v>
+        <v>71750</v>
       </c>
       <c r="N418" s="2" t="inlineStr">
         <is>
@@ -22462,11 +22460,11 @@
       <c r="K419" s="11" t="n">
         <v>50393.5</v>
       </c>
-      <c r="L419" s="25" t="n">
-        <v>-39</v>
+      <c r="L419" s="10" t="n">
+        <v>532</v>
       </c>
       <c r="M419" s="12" t="n">
-        <v>73700</v>
+        <v>71750</v>
       </c>
       <c r="N419" s="8" t="inlineStr">
         <is>
@@ -22517,8 +22515,8 @@
       <c r="K420" s="7" t="n">
         <v>51886.5</v>
       </c>
-      <c r="L420" s="3" t="n">
-        <v>0</v>
+      <c r="L420" s="14" t="n">
+        <v>582</v>
       </c>
       <c r="M420" s="15" t="n">
         <v>71750</v>
@@ -22572,11 +22570,11 @@
       <c r="K421" s="6" t="n">
         <v>-14872</v>
       </c>
-      <c r="L421" s="4" t="n">
-        <v>-129</v>
+      <c r="L421" s="14" t="n">
+        <v>453</v>
       </c>
       <c r="M421" s="15" t="n">
-        <v>78200</v>
+        <v>71750</v>
       </c>
       <c r="N421" s="2" t="inlineStr">
         <is>
@@ -22627,11 +22625,11 @@
       <c r="K422" s="6" t="n">
         <v>-19557.5</v>
       </c>
-      <c r="L422" s="4" t="n">
-        <v>-277</v>
+      <c r="L422" s="14" t="n">
+        <v>305</v>
       </c>
       <c r="M422" s="15" t="n">
-        <v>85600</v>
+        <v>71750</v>
       </c>
       <c r="N422" s="2" t="inlineStr">
         <is>
@@ -22682,8 +22680,8 @@
       <c r="K423" s="11" t="n">
         <v>17712</v>
       </c>
-      <c r="L423" s="9" t="n">
-        <v>0</v>
+      <c r="L423" s="10" t="n">
+        <v>974</v>
       </c>
       <c r="M423" s="12" t="n">
         <v>71750</v>
@@ -22737,11 +22735,11 @@
       <c r="K424" s="6" t="n">
         <v>-27157.5</v>
       </c>
-      <c r="L424" s="4" t="n">
-        <v>-223</v>
+      <c r="L424" s="14" t="n">
+        <v>751</v>
       </c>
       <c r="M424" s="15" t="n">
-        <v>82900</v>
+        <v>71750</v>
       </c>
       <c r="N424" s="2" t="inlineStr">
         <is>
@@ -22792,8 +22790,8 @@
       <c r="K425" s="18" t="n">
         <v>-12246</v>
       </c>
-      <c r="L425" s="9" t="n">
-        <v>0</v>
+      <c r="L425" s="10" t="n">
+        <v>1161</v>
       </c>
       <c r="M425" s="12" t="n">
         <v>71750</v>
@@ -22847,11 +22845,11 @@
       <c r="K426" s="7" t="n">
         <v>13491.5</v>
       </c>
-      <c r="L426" s="4" t="n">
-        <v>-14</v>
+      <c r="L426" s="14" t="n">
+        <v>1147</v>
       </c>
       <c r="M426" s="15" t="n">
-        <v>72450</v>
+        <v>71750</v>
       </c>
       <c r="N426" s="2" t="inlineStr">
         <is>
@@ -22902,8 +22900,8 @@
       <c r="K427" s="11" t="n">
         <v>17371.5</v>
       </c>
-      <c r="L427" s="9" t="n">
-        <v>0</v>
+      <c r="L427" s="10" t="n">
+        <v>1180</v>
       </c>
       <c r="M427" s="12" t="n">
         <v>71750</v>
@@ -22957,11 +22955,11 @@
       <c r="K428" s="6" t="n">
         <v>-13807</v>
       </c>
-      <c r="L428" s="4" t="n">
-        <v>-91</v>
+      <c r="L428" s="14" t="n">
+        <v>1089</v>
       </c>
       <c r="M428" s="15" t="n">
-        <v>76300</v>
+        <v>71750</v>
       </c>
       <c r="N428" s="2" t="inlineStr">
         <is>
@@ -23012,11 +23010,11 @@
       <c r="K429" s="7" t="n">
         <v>1575.5</v>
       </c>
-      <c r="L429" s="6" t="n">
-        <v>-314</v>
+      <c r="L429" s="14" t="n">
+        <v>866</v>
       </c>
       <c r="M429" s="15" t="n">
-        <v>87450</v>
+        <v>71750</v>
       </c>
       <c r="N429" s="2" t="inlineStr">
         <is>
@@ -23067,18 +23065,18 @@
       <c r="K430" s="22" t="n">
         <v>-52975</v>
       </c>
-      <c r="L430" s="22" t="n">
-        <v>-626</v>
-      </c>
-      <c r="M430" s="23" t="n">
-        <v>103050</v>
+      <c r="L430" s="23" t="n">
+        <v>554</v>
+      </c>
+      <c r="M430" s="24" t="n">
+        <v>71750</v>
       </c>
       <c r="N430" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O430" s="24" t="inlineStr">
+      <c r="O430" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -24962,8 +24960,8 @@
       <c r="K467" s="7" t="n">
         <v>40511.5</v>
       </c>
-      <c r="L467" s="3" t="n">
-        <v>0</v>
+      <c r="L467" s="14" t="n">
+        <v>201</v>
       </c>
       <c r="M467" s="15" t="n">
         <v>71750</v>
@@ -25017,11 +25015,11 @@
       <c r="K468" s="6" t="n">
         <v>-929.5</v>
       </c>
-      <c r="L468" s="4" t="n">
-        <v>-69</v>
+      <c r="L468" s="14" t="n">
+        <v>132</v>
       </c>
       <c r="M468" s="15" t="n">
-        <v>75200</v>
+        <v>71750</v>
       </c>
       <c r="N468" s="2" t="inlineStr">
         <is>
@@ -25072,8 +25070,8 @@
       <c r="K469" s="11" t="n">
         <v>10489.5</v>
       </c>
-      <c r="L469" s="9" t="n">
-        <v>0</v>
+      <c r="L469" s="10" t="n">
+        <v>267</v>
       </c>
       <c r="M469" s="12" t="n">
         <v>71750</v>
@@ -25127,8 +25125,8 @@
       <c r="K470" s="7" t="n">
         <v>32690.5</v>
       </c>
-      <c r="L470" s="3" t="n">
-        <v>0</v>
+      <c r="L470" s="14" t="n">
+        <v>724</v>
       </c>
       <c r="M470" s="15" t="n">
         <v>71750</v>
@@ -25182,8 +25180,8 @@
       <c r="K471" s="7" t="n">
         <v>16484.5</v>
       </c>
-      <c r="L471" s="3" t="n">
-        <v>0</v>
+      <c r="L471" s="14" t="n">
+        <v>1564</v>
       </c>
       <c r="M471" s="15" t="n">
         <v>71750</v>
@@ -25237,8 +25235,8 @@
       <c r="K472" s="6" t="n">
         <v>-4792</v>
       </c>
-      <c r="L472" s="3" t="n">
-        <v>0</v>
+      <c r="L472" s="14" t="n">
+        <v>1868</v>
       </c>
       <c r="M472" s="15" t="n">
         <v>71750</v>
@@ -25292,11 +25290,11 @@
       <c r="K473" s="7" t="n">
         <v>11482.5</v>
       </c>
-      <c r="L473" s="4" t="n">
-        <v>-101</v>
+      <c r="L473" s="14" t="n">
+        <v>1767</v>
       </c>
       <c r="M473" s="15" t="n">
-        <v>76800</v>
+        <v>71750</v>
       </c>
       <c r="N473" s="2" t="inlineStr">
         <is>
@@ -25347,11 +25345,11 @@
       <c r="K474" s="11" t="n">
         <v>1614.5</v>
       </c>
-      <c r="L474" s="25" t="n">
-        <v>-159</v>
+      <c r="L474" s="10" t="n">
+        <v>1709</v>
       </c>
       <c r="M474" s="12" t="n">
-        <v>79700</v>
+        <v>71750</v>
       </c>
       <c r="N474" s="8" t="inlineStr">
         <is>
@@ -25402,11 +25400,11 @@
       <c r="K475" s="6" t="n">
         <v>-21379.5</v>
       </c>
-      <c r="L475" s="4" t="n">
-        <v>-161</v>
+      <c r="L475" s="14" t="n">
+        <v>1707</v>
       </c>
       <c r="M475" s="15" t="n">
-        <v>79800</v>
+        <v>71750</v>
       </c>
       <c r="N475" s="2" t="inlineStr">
         <is>
@@ -25457,8 +25455,8 @@
       <c r="K476" s="6" t="n">
         <v>-19240.5</v>
       </c>
-      <c r="L476" s="3" t="n">
-        <v>0</v>
+      <c r="L476" s="14" t="n">
+        <v>1952</v>
       </c>
       <c r="M476" s="15" t="n">
         <v>71750</v>
@@ -25512,8 +25510,8 @@
       <c r="K477" s="6" t="n">
         <v>-18013</v>
       </c>
-      <c r="L477" s="3" t="n">
-        <v>0</v>
+      <c r="L477" s="14" t="n">
+        <v>2125</v>
       </c>
       <c r="M477" s="15" t="n">
         <v>71750</v>
@@ -25567,8 +25565,8 @@
       <c r="K478" s="6" t="n">
         <v>-18457.5</v>
       </c>
-      <c r="L478" s="3" t="n">
-        <v>0</v>
+      <c r="L478" s="14" t="n">
+        <v>2233</v>
       </c>
       <c r="M478" s="15" t="n">
         <v>71750</v>
@@ -25622,10 +25620,10 @@
       <c r="K479" s="22" t="n">
         <v>-24654</v>
       </c>
-      <c r="L479" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M479" s="23" t="n">
+      <c r="L479" s="23" t="n">
+        <v>2301</v>
+      </c>
+      <c r="M479" s="24" t="n">
         <v>71750</v>
       </c>
       <c r="N479" s="19" t="inlineStr">
@@ -25633,7 +25631,7 @@
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O479" s="24" t="inlineStr">
+      <c r="O479" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -25783,8 +25781,8 @@
       <c r="K482" s="7" t="n">
         <v>8710.5</v>
       </c>
-      <c r="L482" s="3" t="n">
-        <v>0</v>
+      <c r="L482" s="14" t="n">
+        <v>191</v>
       </c>
       <c r="M482" s="15" t="n">
         <v>71750</v>
@@ -25838,11 +25836,11 @@
       <c r="K483" s="7" t="n">
         <v>11005</v>
       </c>
-      <c r="L483" s="6" t="n">
-        <v>-427</v>
+      <c r="L483" s="4" t="n">
+        <v>-236</v>
       </c>
       <c r="M483" s="15" t="n">
-        <v>93100</v>
+        <v>83550</v>
       </c>
       <c r="N483" s="2" t="inlineStr">
         <is>
@@ -25893,8 +25891,8 @@
       <c r="K484" s="11" t="n">
         <v>24806</v>
       </c>
-      <c r="L484" s="9" t="n">
-        <v>0</v>
+      <c r="L484" s="10" t="n">
+        <v>376</v>
       </c>
       <c r="M484" s="12" t="n">
         <v>71750</v>
@@ -25948,8 +25946,8 @@
       <c r="K485" s="7" t="n">
         <v>23557.5</v>
       </c>
-      <c r="L485" s="3" t="n">
-        <v>0</v>
+      <c r="L485" s="14" t="n">
+        <v>672</v>
       </c>
       <c r="M485" s="15" t="n">
         <v>71750</v>
@@ -26003,11 +26001,11 @@
       <c r="K486" s="7" t="n">
         <v>6217.5</v>
       </c>
-      <c r="L486" s="4" t="n">
-        <v>-9</v>
+      <c r="L486" s="14" t="n">
+        <v>663</v>
       </c>
       <c r="M486" s="15" t="n">
-        <v>72200</v>
+        <v>71750</v>
       </c>
       <c r="N486" s="2" t="inlineStr">
         <is>
@@ -26058,8 +26056,8 @@
       <c r="K487" s="7" t="n">
         <v>19036</v>
       </c>
-      <c r="L487" s="3" t="n">
-        <v>0</v>
+      <c r="L487" s="14" t="n">
+        <v>1028</v>
       </c>
       <c r="M487" s="15" t="n">
         <v>71750</v>
@@ -26113,8 +26111,8 @@
       <c r="K488" s="7" t="n">
         <v>19613</v>
       </c>
-      <c r="L488" s="3" t="n">
-        <v>0</v>
+      <c r="L488" s="14" t="n">
+        <v>1446</v>
       </c>
       <c r="M488" s="15" t="n">
         <v>71750</v>
@@ -26168,11 +26166,11 @@
       <c r="K489" s="6" t="n">
         <v>-31106.5</v>
       </c>
-      <c r="L489" s="4" t="n">
-        <v>-150</v>
+      <c r="L489" s="14" t="n">
+        <v>1296</v>
       </c>
       <c r="M489" s="15" t="n">
-        <v>79250</v>
+        <v>71750</v>
       </c>
       <c r="N489" s="2" t="inlineStr">
         <is>
@@ -26223,11 +26221,11 @@
       <c r="K490" s="6" t="n">
         <v>-57498</v>
       </c>
-      <c r="L490" s="6" t="n">
-        <v>-680</v>
+      <c r="L490" s="14" t="n">
+        <v>766</v>
       </c>
       <c r="M490" s="15" t="n">
-        <v>105750</v>
+        <v>71750</v>
       </c>
       <c r="N490" s="2" t="inlineStr">
         <is>
@@ -26278,18 +26276,18 @@
       <c r="K491" s="22" t="n">
         <v>-38717</v>
       </c>
-      <c r="L491" s="22" t="n">
-        <v>-1317</v>
-      </c>
-      <c r="M491" s="30" t="n">
-        <v>137600</v>
+      <c r="L491" s="23" t="n">
+        <v>129</v>
+      </c>
+      <c r="M491" s="24" t="n">
+        <v>71750</v>
       </c>
       <c r="N491" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O491" s="24" t="inlineStr">
+      <c r="O491" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -26643,8 +26641,8 @@
       <c r="K498" s="7" t="n">
         <v>13381</v>
       </c>
-      <c r="L498" s="3" t="n">
-        <v>0</v>
+      <c r="L498" s="14" t="n">
+        <v>342</v>
       </c>
       <c r="M498" s="15" t="n">
         <v>71750</v>
@@ -26698,8 +26696,8 @@
       <c r="K499" s="7" t="n">
         <v>23009.5</v>
       </c>
-      <c r="L499" s="3" t="n">
-        <v>0</v>
+      <c r="L499" s="14" t="n">
+        <v>491</v>
       </c>
       <c r="M499" s="15" t="n">
         <v>71750</v>
@@ -26753,8 +26751,8 @@
       <c r="K500" s="11" t="n">
         <v>36180</v>
       </c>
-      <c r="L500" s="9" t="n">
-        <v>0</v>
+      <c r="L500" s="10" t="n">
+        <v>1478</v>
       </c>
       <c r="M500" s="12" t="n">
         <v>71750</v>
@@ -26808,8 +26806,8 @@
       <c r="K501" s="6" t="n">
         <v>-3273</v>
       </c>
-      <c r="L501" s="3" t="n">
-        <v>0</v>
+      <c r="L501" s="14" t="n">
+        <v>2141</v>
       </c>
       <c r="M501" s="15" t="n">
         <v>71750</v>
@@ -26863,8 +26861,8 @@
       <c r="K502" s="6" t="n">
         <v>-10687</v>
       </c>
-      <c r="L502" s="3" t="n">
-        <v>0</v>
+      <c r="L502" s="14" t="n">
+        <v>2255</v>
       </c>
       <c r="M502" s="15" t="n">
         <v>71750</v>
@@ -26918,11 +26916,11 @@
       <c r="K503" s="6" t="n">
         <v>-22696</v>
       </c>
-      <c r="L503" s="6" t="n">
-        <v>-372</v>
+      <c r="L503" s="14" t="n">
+        <v>1883</v>
       </c>
       <c r="M503" s="15" t="n">
-        <v>90350</v>
+        <v>71750</v>
       </c>
       <c r="N503" s="2" t="inlineStr">
         <is>
@@ -26973,11 +26971,11 @@
       <c r="K504" s="6" t="n">
         <v>-35243.5</v>
       </c>
-      <c r="L504" s="6" t="n">
-        <v>-1279</v>
-      </c>
-      <c r="M504" s="29" t="n">
-        <v>135700</v>
+      <c r="L504" s="14" t="n">
+        <v>976</v>
+      </c>
+      <c r="M504" s="15" t="n">
+        <v>71750</v>
       </c>
       <c r="N504" s="2" t="inlineStr">
         <is>
@@ -27029,17 +27027,17 @@
         <v>-84673</v>
       </c>
       <c r="L505" s="22" t="n">
-        <v>-2770</v>
-      </c>
-      <c r="M505" s="30" t="n">
-        <v>210250</v>
+        <v>-515</v>
+      </c>
+      <c r="M505" s="24" t="n">
+        <v>97500</v>
       </c>
       <c r="N505" s="19" t="inlineStr">
         <is>
           <t>🔴翻空</t>
         </is>
       </c>
-      <c r="O505" s="24" t="inlineStr">
+      <c r="O505" s="25" t="inlineStr">
         <is>
           <t>👉 隔天出場</t>
         </is>
@@ -27773,7 +27771,7 @@
       <c r="I2" s="3" t="n">
         <v>268336</v>
       </c>
-      <c r="J2" s="31" t="n">
+      <c r="J2" s="29" t="n">
         <v>78.90000000000001</v>
       </c>
       <c r="K2" s="16" t="inlineStr">
@@ -27814,7 +27812,7 @@
       <c r="I3" s="3" t="n">
         <v>270222</v>
       </c>
-      <c r="J3" s="31" t="n">
+      <c r="J3" s="29" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="K3" s="16" t="inlineStr">
@@ -27855,7 +27853,7 @@
       <c r="I4" s="3" t="n">
         <v>310408</v>
       </c>
-      <c r="J4" s="31" t="n">
+      <c r="J4" s="29" t="n">
         <v>106.9</v>
       </c>
       <c r="K4" s="16" t="inlineStr">
@@ -27896,10 +27894,10 @@
       <c r="I5" s="3" t="n">
         <v>302244</v>
       </c>
-      <c r="J5" s="31" t="n">
+      <c r="J5" s="29" t="n">
         <v>101.5</v>
       </c>
-      <c r="K5" s="32" t="inlineStr">
+      <c r="K5" s="30" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
@@ -27937,7 +27935,7 @@
       <c r="I6" s="3" t="n">
         <v>323030</v>
       </c>
-      <c r="J6" s="31" t="n">
+      <c r="J6" s="29" t="n">
         <v>115.4</v>
       </c>
       <c r="K6" s="16" t="inlineStr">
@@ -27978,10 +27976,10 @@
       <c r="I7" s="3" t="n">
         <v>295666</v>
       </c>
-      <c r="J7" s="31" t="n">
+      <c r="J7" s="29" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="K7" s="32" t="inlineStr">
+      <c r="K7" s="30" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
@@ -28019,10 +28017,10 @@
       <c r="I8" s="3" t="n">
         <v>286802</v>
       </c>
-      <c r="J8" s="31" t="n">
+      <c r="J8" s="29" t="n">
         <v>91.2</v>
       </c>
-      <c r="K8" s="32" t="inlineStr">
+      <c r="K8" s="30" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
@@ -28060,7 +28058,7 @@
       <c r="I9" s="3" t="n">
         <v>326038</v>
       </c>
-      <c r="J9" s="31" t="n">
+      <c r="J9" s="29" t="n">
         <v>117.4</v>
       </c>
       <c r="K9" s="16" t="inlineStr">
@@ -28101,7 +28099,7 @@
       <c r="I10" s="3" t="n">
         <v>432624</v>
       </c>
-      <c r="J10" s="31" t="n">
+      <c r="J10" s="29" t="n">
         <v>188.4</v>
       </c>
       <c r="K10" s="16" t="inlineStr">
@@ -28142,7 +28140,7 @@
       <c r="I11" s="3" t="n">
         <v>531610</v>
       </c>
-      <c r="J11" s="31" t="n">
+      <c r="J11" s="29" t="n">
         <v>254.4</v>
       </c>
       <c r="K11" s="16" t="inlineStr">
@@ -28183,10 +28181,10 @@
       <c r="I12" s="3" t="n">
         <v>528496</v>
       </c>
-      <c r="J12" s="31" t="n">
+      <c r="J12" s="29" t="n">
         <v>252.3</v>
       </c>
-      <c r="K12" s="32" t="inlineStr">
+      <c r="K12" s="30" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
@@ -28224,7 +28222,7 @@
       <c r="I13" s="3" t="n">
         <v>588982</v>
       </c>
-      <c r="J13" s="31" t="n">
+      <c r="J13" s="29" t="n">
         <v>292.7</v>
       </c>
       <c r="K13" s="16" t="inlineStr">
@@ -28265,7 +28263,7 @@
       <c r="I14" s="3" t="n">
         <v>626818</v>
       </c>
-      <c r="J14" s="31" t="n">
+      <c r="J14" s="29" t="n">
         <v>317.9</v>
       </c>
       <c r="K14" s="16" t="inlineStr">
@@ -28306,7 +28304,7 @@
       <c r="I15" s="3" t="n">
         <v>758354</v>
       </c>
-      <c r="J15" s="31" t="n">
+      <c r="J15" s="29" t="n">
         <v>405.6</v>
       </c>
       <c r="K15" s="16" t="inlineStr">
@@ -28347,7 +28345,7 @@
       <c r="I16" s="3" t="n">
         <v>803490</v>
       </c>
-      <c r="J16" s="31" t="n">
+      <c r="J16" s="29" t="n">
         <v>435.7</v>
       </c>
       <c r="K16" s="16" t="inlineStr">
@@ -28388,7 +28386,7 @@
       <c r="I17" s="3" t="n">
         <v>831476</v>
       </c>
-      <c r="J17" s="31" t="n">
+      <c r="J17" s="29" t="n">
         <v>454.3</v>
       </c>
       <c r="K17" s="16" t="inlineStr">
@@ -28398,31 +28396,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B18" s="33" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>16筆</t>
         </is>
       </c>
-      <c r="E18" s="33" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>勝率75.0%</t>
         </is>
       </c>
-      <c r="F18" s="34" t="n">
+      <c r="F18" s="32" t="n">
         <v>13666</v>
       </c>
-      <c r="G18" s="34" t="n">
+      <c r="G18" s="32" t="n">
         <v>681476</v>
       </c>
-      <c r="I18" s="34" t="n">
+      <c r="I18" s="32" t="n">
         <v>831476</v>
       </c>
-      <c r="J18" s="35" t="n">
+      <c r="J18" s="33" t="n">
         <v>454.3</v>
       </c>
     </row>
@@ -29091,72 +29089,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="36" t="inlineStr">
+      <c r="B1" s="34" t="inlineStr">
         <is>
           <t>近月_ours</t>
         </is>
       </c>
-      <c r="C1" s="36" t="inlineStr">
+      <c r="C1" s="34" t="inlineStr">
         <is>
           <t>近月_correct</t>
         </is>
       </c>
-      <c r="D1" s="36" t="inlineStr">
+      <c r="D1" s="34" t="inlineStr">
         <is>
           <t>近月_diff</t>
         </is>
       </c>
-      <c r="E1" s="36" t="inlineStr">
+      <c r="E1" s="34" t="inlineStr">
         <is>
           <t>遠月_ours</t>
         </is>
       </c>
-      <c r="F1" s="36" t="inlineStr">
+      <c r="F1" s="34" t="inlineStr">
         <is>
           <t>遠月_correct</t>
         </is>
       </c>
-      <c r="G1" s="36" t="inlineStr">
+      <c r="G1" s="34" t="inlineStr">
         <is>
           <t>遠月_diff</t>
         </is>
       </c>
-      <c r="H1" s="36" t="inlineStr">
+      <c r="H1" s="34" t="inlineStr">
         <is>
           <t>小散戶_ours</t>
         </is>
       </c>
-      <c r="I1" s="36" t="inlineStr">
+      <c r="I1" s="34" t="inlineStr">
         <is>
           <t>小散戶_correct</t>
         </is>
       </c>
-      <c r="J1" s="36" t="inlineStr">
+      <c r="J1" s="34" t="inlineStr">
         <is>
           <t>小散戶_diff</t>
         </is>
       </c>
-      <c r="K1" s="36" t="inlineStr">
+      <c r="K1" s="34" t="inlineStr">
         <is>
           <t>主力_ours</t>
         </is>
       </c>
-      <c r="L1" s="36" t="inlineStr">
+      <c r="L1" s="34" t="inlineStr">
         <is>
           <t>主力_correct</t>
         </is>
       </c>
-      <c r="M1" s="36" t="inlineStr">
+      <c r="M1" s="34" t="inlineStr">
         <is>
           <t>主力_diff</t>
         </is>
       </c>
-      <c r="N1" s="36" t="inlineStr">
+      <c r="N1" s="34" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
@@ -29372,7 +29370,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>台指期籌碼策略（v2 優化版）</t>
         </is>
@@ -29382,7 +29380,7 @@
       <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="38" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>【資料來源】100% 期交所</t>
         </is>
@@ -29413,7 +29411,7 @@
       <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>【公式】</t>
         </is>
@@ -29458,7 +29456,7 @@
       <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>【策略（v2 優化版）】</t>
         </is>
@@ -29489,7 +29487,7 @@
       <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>【信號說明】</t>
         </is>
@@ -29548,7 +29546,7 @@
       <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>【操作欄說明】</t>
         </is>
@@ -29596,7 +29594,7 @@
       <c r="A36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="38" t="inlineStr">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>【改善原因】</t>
         </is>
@@ -29620,7 +29618,7 @@
       <c r="A40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="38" t="inlineStr">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>【成本】</t>
         </is>

--- a/output/台指期籌碼追蹤.xlsx
+++ b/output/台指期籌碼追蹤.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O517"/>
+  <dimension ref="A1:O518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -646,9 +646,7 @@
       <c r="J2" s="4" t="n">
         <v>-10845</v>
       </c>
-      <c r="K2" s="3" t="n">
-        <v/>
-      </c>
+      <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
@@ -695,9 +693,7 @@
       <c r="J3" s="4" t="n">
         <v>-52403</v>
       </c>
-      <c r="K3" s="3" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
@@ -744,9 +740,7 @@
       <c r="J4" s="4" t="n">
         <v>-32058</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
@@ -793,9 +787,7 @@
       <c r="J5" s="4" t="n">
         <v>-33290</v>
       </c>
-      <c r="K5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
@@ -842,9 +834,7 @@
       <c r="J6" s="4" t="n">
         <v>-27945.5</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
@@ -27650,6 +27640,57 @@
         </is>
       </c>
       <c r="O517" s="5" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>2026/03/23</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="C518" s="3" t="n">
+        <v>32501</v>
+      </c>
+      <c r="D518" s="3" t="n">
+        <v>32532</v>
+      </c>
+      <c r="E518" s="3" t="n">
+        <v>5423</v>
+      </c>
+      <c r="F518" s="3" t="n">
+        <v>4923</v>
+      </c>
+      <c r="G518" s="3" t="n">
+        <v>4976</v>
+      </c>
+      <c r="H518" s="3" t="n">
+        <v>35105</v>
+      </c>
+      <c r="I518" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="J518" s="4" t="n">
+        <v>-37619.5</v>
+      </c>
+      <c r="K518" s="6" t="n">
+        <v>-3651.5</v>
+      </c>
+      <c r="L518" s="2" t="inlineStr"/>
+      <c r="M518" s="2" t="inlineStr"/>
+      <c r="N518" s="2" t="inlineStr">
+        <is>
+          <t>⬇️空方 ⚠️危險</t>
+        </is>
+      </c>
+      <c r="O518" s="5" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
@@ -29376,9 +29417,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="36" t="inlineStr">
         <is>
@@ -29407,9 +29446,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="36" t="inlineStr">
         <is>
@@ -29452,9 +29489,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
@@ -29483,9 +29518,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="36" t="inlineStr">
         <is>
@@ -29542,9 +29575,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="36" t="inlineStr">
         <is>
@@ -29580,9 +29611,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -29590,9 +29619,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="36" t="inlineStr">
         <is>
@@ -29614,9 +29641,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="36" t="inlineStr">
         <is>

--- a/output/台指期籌碼追蹤.xlsx
+++ b/output/台指期籌碼追蹤.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O518"/>
+  <dimension ref="A1:O519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27691,6 +27691,57 @@
         </is>
       </c>
       <c r="O518" s="5" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>2026/03/24</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>二</t>
+        </is>
+      </c>
+      <c r="C519" s="3" t="n">
+        <v>33280</v>
+      </c>
+      <c r="D519" s="3" t="n">
+        <v>32771</v>
+      </c>
+      <c r="E519" s="3" t="n">
+        <v>15855</v>
+      </c>
+      <c r="F519" s="3" t="n">
+        <v>15675</v>
+      </c>
+      <c r="G519" s="3" t="n">
+        <v>-2627</v>
+      </c>
+      <c r="H519" s="3" t="n">
+        <v>27627</v>
+      </c>
+      <c r="I519" s="3" t="n">
+        <v>18482</v>
+      </c>
+      <c r="J519" s="4" t="n">
+        <v>-17162.5</v>
+      </c>
+      <c r="K519" s="6" t="n">
+        <v>-638</v>
+      </c>
+      <c r="L519" s="2" t="inlineStr"/>
+      <c r="M519" s="2" t="inlineStr"/>
+      <c r="N519" s="2" t="inlineStr">
+        <is>
+          <t>⬇️空方</t>
+        </is>
+      </c>
+      <c r="O519" s="5" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
@@ -29417,7 +29468,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="36" t="inlineStr">
         <is>
@@ -29446,7 +29496,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="36" t="inlineStr">
         <is>
@@ -29489,7 +29538,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
@@ -29518,7 +29566,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="36" t="inlineStr">
         <is>
@@ -29575,7 +29622,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="36" t="inlineStr">
         <is>
@@ -29611,7 +29657,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -29619,7 +29664,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="36" t="inlineStr">
         <is>
@@ -29641,7 +29685,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="36" t="inlineStr">
         <is>

--- a/output/台指期籌碼追蹤.xlsx
+++ b/output/台指期籌碼追蹤.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O519"/>
+  <dimension ref="A1:O520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27742,6 +27742,57 @@
         </is>
       </c>
       <c r="O519" s="5" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>2026/03/25</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="C520" s="3" t="n">
+        <v>33786</v>
+      </c>
+      <c r="D520" s="3" t="n">
+        <v>33638</v>
+      </c>
+      <c r="E520" s="3" t="n">
+        <v>14868</v>
+      </c>
+      <c r="F520" s="3" t="n">
+        <v>13912</v>
+      </c>
+      <c r="G520" s="3" t="n">
+        <v>-2525</v>
+      </c>
+      <c r="H520" s="3" t="n">
+        <v>18377</v>
+      </c>
+      <c r="I520" s="3" t="n">
+        <v>17393</v>
+      </c>
+      <c r="J520" s="4" t="n">
+        <v>-8896</v>
+      </c>
+      <c r="K520" s="6" t="n">
+        <v>-8849.5</v>
+      </c>
+      <c r="L520" s="2" t="inlineStr"/>
+      <c r="M520" s="2" t="inlineStr"/>
+      <c r="N520" s="2" t="inlineStr">
+        <is>
+          <t>⬇️空方</t>
+        </is>
+      </c>
+      <c r="O520" s="5" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
